--- a/Horarios/HorarioWAN_2025.xlsx
+++ b/Horarios/HorarioWAN_2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L00614578\Documents\Github\WAN\Horarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F546CF1-E622-47D1-8F12-8E309B23C23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB678E8C-429A-40DA-9421-5CC9BDF46AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="WAN_201" sheetId="2" r:id="rId2"/>
     <sheet name="WAN_301" sheetId="4" r:id="rId3"/>
+    <sheet name="WAN_201_Canvas" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="66">
   <si>
     <t>3:00 - 4:00</t>
   </si>
@@ -229,9 +230,6 @@
     <t>AVANCE DEL RETO / RETROALIMENTACIÓN</t>
   </si>
   <si>
-    <t>PRESENTACIÓN DEL RETO CON EL SOCIO FORMADOR</t>
-  </si>
-  <si>
     <t>EXAMEN MÓDULO 1</t>
   </si>
   <si>
@@ -326,6 +324,51 @@
       </rPr>
       <t xml:space="preserve"> (28 de Abril - 2 de Mayo)</t>
     </r>
+  </si>
+  <si>
+    <t>24 de Marzo 15:00 horas visita de Citlalli Feregrino</t>
+  </si>
+  <si>
+    <t>PRESENTACIÓN DEL RETO CON EL SOCIO FORMADOR / RETO</t>
+  </si>
+  <si>
+    <t>9 de Abril 15:00 horas visita de Citlalli Feregrino</t>
+  </si>
+  <si>
+    <t>2 de Mayo 15:00 horas visita de Citlalli Feregrino</t>
+  </si>
+  <si>
+    <t>25 de Abril 15:00 horas presentación de avance de reto</t>
+  </si>
+  <si>
+    <t>4 de Abril 15:00 horas presentación de avance de reto</t>
+  </si>
+  <si>
+    <t>28 de Marzo 17:00 horas presentación de avance de reto</t>
+  </si>
+  <si>
+    <t>Evaluación de los estudiantes por partes de profesores y socio formador</t>
+  </si>
+  <si>
+    <t>Coevaluación de los estudiantes</t>
+  </si>
+  <si>
+    <t>Liz</t>
+  </si>
+  <si>
+    <t>Lunes</t>
+  </si>
+  <si>
+    <t>Miércoles</t>
+  </si>
+  <si>
+    <t>3:00 a 5:00</t>
+  </si>
+  <si>
+    <t>Viernes</t>
+  </si>
+  <si>
+    <t>3:00 a 5:30</t>
   </si>
 </sst>
 </file>
@@ -525,19 +568,70 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -549,16 +643,58 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -567,100 +703,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1898,21 +1941,24 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G44"/>
+  <dimension ref="B1:T49"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="10.90625" style="3"/>
-    <col min="3" max="6" width="12.6328125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="19.7265625" style="3" customWidth="1"/>
+    <col min="3" max="4" width="12.6328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="20.7265625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B2" s="5"/>
       <c r="C2" s="4" t="s">
         <v>6</v>
@@ -1929,93 +1975,132 @@
       <c r="G2" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="R2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="35" t="s">
+      <c r="C3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="35" t="s">
+      <c r="F3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="13" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="I3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3">
+        <f>2.5+2.5+2.5+2.5+2</f>
+        <v>12</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>60</v>
+      </c>
+      <c r="R3" t="s">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="28"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C4" s="10"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
+      <c r="I4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4">
+        <f>2.5+2.5+2.5</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="29" t="s">
+      <c r="C5" s="10"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="6" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="29"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="29"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="6"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B10" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
       <c r="C11" s="4" t="s">
         <v>6</v>
@@ -2033,90 +2118,121 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="33" t="s">
+      <c r="E12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="F12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="10" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="I12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" t="s">
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <f>3+2.5+3+2</f>
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="29"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C13" s="15"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="10"/>
+      <c r="N13" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="53" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="D14" s="18"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="N14" t="s">
+        <v>20</v>
+      </c>
+      <c r="O14">
+        <f>2+2.5+2+2</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="33" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="53"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E15" s="40"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="28"/>
+      <c r="N15" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="10" t="s">
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="53"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="F16" s="17"/>
+      <c r="G16" s="28"/>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="11"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="18"/>
       <c r="G17" s="7"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B19" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B20" s="5"/>
       <c r="C20" s="4" t="s">
         <v>6</v>
@@ -2133,89 +2249,130 @@
       <c r="G20" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="R20" t="s">
+        <v>62</v>
+      </c>
+      <c r="S20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="E21" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="G21" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N21" t="s">
+        <v>23</v>
+      </c>
+      <c r="O21">
+        <f>2.5+3</f>
+        <v>5.5</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>60</v>
+      </c>
+      <c r="R21" t="s">
+        <v>65</v>
+      </c>
+      <c r="S21" t="s">
+        <v>63</v>
+      </c>
+      <c r="T21">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="30"/>
-    </row>
-    <row r="23" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C22" s="37"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="21"/>
+      <c r="I22" s="2"/>
+      <c r="N22" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22">
+        <f>2.5+2</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="38"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="30"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="G23" s="21"/>
+      <c r="N23" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23">
+        <f>5+4</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="15" t="s">
+      <c r="C24" s="38"/>
+      <c r="D24" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="30"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E24" s="17"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="21"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="31"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C25" s="38"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="22"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="7"/>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B28" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B29" s="5"/>
       <c r="C29" s="4" t="s">
         <v>6</v>
@@ -2232,91 +2389,127 @@
       <c r="G29" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R29" t="s">
+        <v>64</v>
+      </c>
+      <c r="T29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="20" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="I30" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" t="s">
+        <v>23</v>
+      </c>
+      <c r="O30">
+        <f>3+2.5+2+3</f>
+        <v>10.5</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>60</v>
+      </c>
+      <c r="R30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="30"/>
-    </row>
-    <row r="32" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="31"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="21"/>
+      <c r="N31" t="s">
+        <v>20</v>
+      </c>
+      <c r="O31">
+        <f>2+2.5+2</f>
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="54" t="s">
+      <c r="D32" s="31"/>
+      <c r="E32" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="30"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="G32" s="21"/>
+      <c r="N32" t="s">
+        <v>24</v>
+      </c>
+      <c r="O32">
+        <f>3+4</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="15" t="s">
+      <c r="C33" s="33"/>
+      <c r="D33" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="30"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E33" s="41"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="21"/>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="31"/>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="52"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="25"/>
       <c r="G35" s="7"/>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B37" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B38" s="5"/>
       <c r="C38" s="4" t="s">
         <v>6</v>
@@ -2333,98 +2526,203 @@
       <c r="G38" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="2:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R38" t="s">
+        <v>62</v>
+      </c>
+      <c r="S38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="21" t="s">
+      <c r="E39" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="20" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="I39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="N39" t="s">
+        <v>23</v>
+      </c>
+      <c r="O39">
+        <f>3+3</f>
+        <v>6</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>60</v>
+      </c>
+      <c r="R39" t="s">
+        <v>63</v>
+      </c>
+      <c r="S39" t="s">
+        <v>65</v>
+      </c>
+      <c r="T39">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="16"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="30"/>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C40" s="33"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="21"/>
+      <c r="I40" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="N40" t="s">
+        <v>20</v>
+      </c>
+      <c r="O40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="19" t="s">
+      <c r="C41" s="33"/>
+      <c r="D41" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="30"/>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="21"/>
+      <c r="I41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="N41" t="s">
+        <v>24</v>
+      </c>
+      <c r="O41">
+        <f>2+5+4</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="30"/>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C42" s="34"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="21"/>
+      <c r="T42">
+        <f>SUM(T3:T39)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="31"/>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="C43" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="27"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="22"/>
+      <c r="O43">
+        <f>SUM(O3:O41)</f>
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="41"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
       <c r="G44" s="7"/>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="M45" t="s">
+        <v>19</v>
+      </c>
+      <c r="N45">
+        <f>O3+O12</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="M46" t="s">
+        <v>23</v>
+      </c>
+      <c r="N46">
+        <f>O13+O21+O30+O39</f>
+        <v>25</v>
+      </c>
+      <c r="O46">
+        <f>SUM(N45:N46)</f>
+        <v>47.5</v>
+      </c>
+      <c r="Q46">
+        <f>O46+T42</f>
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="M47" t="s">
+        <v>20</v>
+      </c>
+      <c r="N47">
+        <f>O4+O14+O22+O31+O40</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="M48" t="s">
+        <v>24</v>
+      </c>
+      <c r="N48">
+        <f>O5+O15+O23+O32+O41</f>
+        <v>33.5</v>
+      </c>
+    </row>
+    <row r="49" spans="14:14" x14ac:dyDescent="0.35">
+      <c r="N49">
+        <f>SUM(N45:N48)</f>
+        <v>110</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E12:E17"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D41:D44"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="G5:G7"/>
     <mergeCell ref="G39:G43"/>
@@ -2436,26 +2734,26 @@
     <mergeCell ref="G21:G25"/>
     <mergeCell ref="G12:G13"/>
     <mergeCell ref="G14:G16"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="D41:D44"/>
-    <mergeCell ref="E39:E44"/>
     <mergeCell ref="F39:F44"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="C23:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="54" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2502,19 +2800,19 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="35" t="s">
+      <c r="E3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2522,21 +2820,21 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="28"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="29" t="s">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="10" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2544,38 +2842,38 @@
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="28" t="s">
+      <c r="B6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="29"/>
+      <c r="F6" s="10"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="29"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="6"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2605,19 +2903,19 @@
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="10" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2625,60 +2923,60 @@
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="34"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="12"/>
       <c r="E13" s="40"/>
-      <c r="F13" s="29"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="34"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="12"/>
       <c r="E14" s="40"/>
-      <c r="F14" s="28" t="s">
-        <v>44</v>
+      <c r="F14" s="13" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="33" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="29" t="s">
+      <c r="D15" s="10" t="s">
         <v>22</v>
       </c>
       <c r="E15" s="40"/>
-      <c r="F15" s="28"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="10" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="28"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="11"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="15"/>
       <c r="F17" s="7"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -2708,19 +3006,19 @@
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="20" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2728,58 +3026,58 @@
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="30"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="19" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="30"/>
+      <c r="F23" s="21"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="15" t="s">
+      <c r="B24" s="17"/>
+      <c r="C24" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="30"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="21"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="31"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="22"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="14"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="18"/>
       <c r="F26" s="7"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -2809,19 +3107,19 @@
       <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="20" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2829,58 +3127,58 @@
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="30"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="21"/>
     </row>
     <row r="32" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="15" t="s">
+      <c r="B32" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="22" t="s">
+      <c r="C32" s="31"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="30"/>
+      <c r="F32" s="21"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="15" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="30"/>
+      <c r="D33" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="55"/>
+      <c r="F33" s="21"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
       <c r="D34" s="40"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="31"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="22"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="27"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="42"/>
       <c r="F35" s="7"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -2910,14 +3208,14 @@
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B39" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="18" t="s">
-        <v>45</v>
+      <c r="D39" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="E39" s="43" t="s">
         <v>26</v>
@@ -2930,59 +3228,59 @@
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="42"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="30"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="44"/>
-      <c r="F40" s="46"/>
+      <c r="F40" s="50"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="42"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="30"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="44"/>
-      <c r="F41" s="46"/>
+      <c r="F41" s="50"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="42"/>
-      <c r="C42" s="15" t="s">
+      <c r="B42" s="52"/>
+      <c r="C42" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="30"/>
+      <c r="D42" s="21"/>
       <c r="E42" s="44"/>
-      <c r="F42" s="46"/>
+      <c r="F42" s="50"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="30"/>
+      <c r="B43" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="33"/>
+      <c r="D43" s="21"/>
       <c r="E43" s="44"/>
-      <c r="F43" s="47"/>
+      <c r="F43" s="51"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="23"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="31"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="22"/>
       <c r="E44" s="45"/>
       <c r="F44" s="7"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -3010,84 +3308,76 @@
       <c r="B48" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B49" s="44"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B50" s="44"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="49"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B51" s="44"/>
-      <c r="C51" s="49"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B52" s="44"/>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B53" s="45"/>
-      <c r="C53" s="50"/>
-      <c r="D53" s="50"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="48"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="F14:F16"/>
     <mergeCell ref="D15:D17"/>
@@ -3104,19 +3394,605 @@
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="E12:E15"/>
     <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="B43:B44"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D245C25-8B0C-4D25-91BE-BA452BDCC89A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:I44"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" style="3"/>
+    <col min="3" max="4" width="12.6328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="14.26953125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="20.7265625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="4.36328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B1" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B2" s="5"/>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="10"/>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B10" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B11" s="5"/>
+      <c r="C11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="10"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="17"/>
+      <c r="D15" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="28"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="17"/>
+      <c r="G16" s="28"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B19" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B20" s="5"/>
+      <c r="C20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B21" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B22" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="37"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="21"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="38"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="21"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="38"/>
+      <c r="D24" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="21"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="38"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="22"/>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="39"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="7"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B28" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B29" s="5"/>
+      <c r="C29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B31" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C31" s="31"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="31"/>
+      <c r="E32" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="21"/>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B33" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="33"/>
+      <c r="D33" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E33" s="41"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="21"/>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B37" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B38" s="5"/>
+      <c r="C38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B40" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="33"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="21"/>
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B41" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="33"/>
+      <c r="D41" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="21"/>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="34"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="21"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B43" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="27"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="22"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.35">
+      <c r="B44" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="30"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="D41:D44"/>
+    <mergeCell ref="C43:C44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Horarios/HorarioWAN_2025.xlsx
+++ b/Horarios/HorarioWAN_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L00614578\Documents\Github\WAN\Horarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB678E8C-429A-40DA-9421-5CC9BDF46AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4F5B43-EF6F-46D4-B0CC-AA0BFC17ABFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -568,103 +568,109 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -697,13 +703,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1983,19 +1983,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="30" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2022,11 +2022,11 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="30"/>
       <c r="I4" s="2" t="s">
         <v>57</v>
       </c>
@@ -2042,11 +2042,11 @@
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="10" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="31" t="s">
         <v>42</v>
       </c>
       <c r="N5" t="s">
@@ -2061,38 +2061,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="10"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
@@ -2122,19 +2122,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="31" t="s">
         <v>42</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -2152,11 +2152,11 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="31"/>
       <c r="N13" t="s">
         <v>23</v>
       </c>
@@ -2168,15 +2168,15 @@
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="32" t="s">
+      <c r="D14" s="15"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="37" t="s">
         <v>43</v>
       </c>
       <c r="N14" t="s">
@@ -2191,13 +2191,13 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="16" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="28"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="37"/>
       <c r="N15" t="s">
         <v>24</v>
       </c>
@@ -2209,22 +2209,22 @@
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="14" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="28"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="37"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="18"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="15"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.35">
@@ -2260,19 +2260,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="G21" s="13" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -2302,11 +2302,11 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="21"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="32"/>
       <c r="I22" s="2"/>
       <c r="N22" t="s">
         <v>20</v>
@@ -2320,13 +2320,13 @@
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="26" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="21"/>
+      <c r="G23" s="32"/>
       <c r="N23" t="s">
         <v>24</v>
       </c>
@@ -2339,32 +2339,32 @@
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="18"/>
+      <c r="D24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="21"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="32"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="22"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="33"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.35">
@@ -2400,19 +2400,19 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="13" t="s">
         <v>42</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -2436,11 +2436,11 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="21"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="32"/>
       <c r="N31" t="s">
         <v>20</v>
       </c>
@@ -2453,17 +2453,17 @@
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="23" t="s">
+      <c r="D32" s="24"/>
+      <c r="E32" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="21"/>
+      <c r="G32" s="32"/>
       <c r="N32" t="s">
         <v>24</v>
       </c>
@@ -2476,32 +2476,32 @@
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="32" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="32"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="22"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="33"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="25"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.35">
@@ -2537,19 +2537,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="29" t="s">
+      <c r="E39" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="13" t="s">
         <v>36</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -2579,11 +2579,11 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="21"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="32"/>
       <c r="I40" s="2" t="s">
         <v>58</v>
       </c>
@@ -2598,13 +2598,13 @@
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="33"/>
-      <c r="D41" s="26" t="s">
+      <c r="C41" s="11"/>
+      <c r="D41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="21"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="32"/>
       <c r="I41" s="2" t="s">
         <v>59</v>
       </c>
@@ -2620,11 +2620,11 @@
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="21"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="32"/>
       <c r="T42">
         <f>SUM(T3:T39)</f>
         <v>12</v>
@@ -2634,13 +2634,13 @@
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="27"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="22"/>
+      <c r="C43" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="29"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="33"/>
       <c r="O43">
         <f>SUM(O3:O41)</f>
         <v>110</v>
@@ -2650,10 +2650,10 @@
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="30"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.35">
@@ -2708,6 +2708,34 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F17"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="E21:E26"/>
     <mergeCell ref="C21:C26"/>
@@ -2723,34 +2751,6 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="D41:D44"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="54" orientation="portrait" r:id="rId1"/>
@@ -2800,19 +2800,19 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="30" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2820,21 +2820,21 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13"/>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="30"/>
     </row>
     <row r="5" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="10" t="s">
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="31" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2842,38 +2842,38 @@
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="10"/>
+      <c r="F6" s="31"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="10"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="31"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
       <c r="F8" s="6"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2903,19 +2903,19 @@
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="31" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2923,23 +2923,23 @@
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="10"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="31"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="13" t="s">
+      <c r="C14" s="15"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="30" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2947,36 +2947,36 @@
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="16" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="13"/>
+      <c r="D15" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="42"/>
+      <c r="F15" s="30"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="14" t="s">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="13"/>
+      <c r="F16" s="30"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="7"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -3006,19 +3006,19 @@
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="F21" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3026,58 +3026,58 @@
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="21"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="32"/>
     </row>
     <row r="23" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="26" t="s">
+      <c r="C23" s="15"/>
+      <c r="D23" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="21"/>
+      <c r="F23" s="32"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="32" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="32"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="22"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="33"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="18"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="15"/>
       <c r="F26" s="7"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3107,19 +3107,19 @@
       <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="F30" s="13" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3127,58 +3127,58 @@
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="21"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="32"/>
     </row>
     <row r="32" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="53" t="s">
+      <c r="C32" s="24"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="21"/>
+      <c r="F32" s="32"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="55"/>
-      <c r="F33" s="21"/>
+      <c r="D33" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="44"/>
+      <c r="F33" s="32"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="22"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="33"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="42"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="22"/>
       <c r="F35" s="7"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3208,19 +3208,19 @@
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="43" t="s">
+      <c r="E39" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="43" t="s">
+      <c r="F39" s="45" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3228,54 +3228,54 @@
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="52"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="50"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="52"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="52"/>
-      <c r="C41" s="31"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="50"/>
+      <c r="B41" s="54"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="52"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="52"/>
-      <c r="C42" s="32" t="s">
+      <c r="B42" s="54"/>
+      <c r="C42" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="21"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="50"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="52"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="21"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="51"/>
+      <c r="B43" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="11"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="53"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="54"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="45"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="47"/>
       <c r="F44" s="7"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3305,79 +3305,87 @@
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="43" t="s">
+      <c r="B48" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="44"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="49"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="51"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="44"/>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="49"/>
-      <c r="F50" s="49"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="49"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="44"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="49"/>
-      <c r="F51" s="49"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="44"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="51"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="45"/>
-      <c r="C53" s="48"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
+      <c r="B53" s="47"/>
+      <c r="C53" s="50"/>
+      <c r="D53" s="50"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E30:E31"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="F14:F16"/>
     <mergeCell ref="D15:D17"/>
@@ -3394,27 +3402,19 @@
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="E12:E15"/>
     <mergeCell ref="B14:B17"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3465,19 +3465,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="30" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2"/>
@@ -3486,22 +3486,22 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="30"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="10" t="s">
+      <c r="C5" s="31"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="31" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3509,38 +3509,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="10"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
@@ -3570,19 +3570,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="31" t="s">
         <v>42</v>
       </c>
       <c r="I12" s="2"/>
@@ -3591,25 +3591,25 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="32" t="s">
+      <c r="D14" s="15"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="37" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3617,34 +3617,34 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="16" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="28"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="37"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="14" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="28"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="37"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="18"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="15"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
@@ -3674,19 +3674,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="G21" s="13" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2"/>
@@ -3695,55 +3695,55 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="37"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="21"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="32"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="26" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="21"/>
+      <c r="G23" s="32"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="18"/>
+      <c r="D24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="21"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="32"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="22"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="33"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
@@ -3773,19 +3773,19 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="32" t="s">
+      <c r="E30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="G30" s="13" t="s">
         <v>42</v>
       </c>
       <c r="I30" s="2"/>
@@ -3794,58 +3794,58 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="21"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="32"/>
     </row>
     <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="23" t="s">
+      <c r="D32" s="24"/>
+      <c r="E32" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="21"/>
+      <c r="G32" s="32"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="32" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="32"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="22"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="33"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="25"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
@@ -3875,19 +3875,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="29" t="s">
+      <c r="E39" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="20" t="s">
+      <c r="G39" s="13" t="s">
         <v>36</v>
       </c>
       <c r="I39" s="2"/>
@@ -3896,60 +3896,93 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="21"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="32"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="33"/>
-      <c r="D41" s="26" t="s">
+      <c r="C41" s="11"/>
+      <c r="D41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="21"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="32"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="21"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="32"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="27"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="22"/>
+      <c r="C43" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="29"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="33"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="30"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
       <c r="G44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="C39:C42"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="D41:D44"/>
+    <mergeCell ref="C43:C44"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="D3:D5"/>
     <mergeCell ref="E3:E5"/>
@@ -3960,39 +3993,6 @@
     <mergeCell ref="D6:D8"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="D41:D44"/>
-    <mergeCell ref="C43:C44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Horarios/HorarioWAN_2025.xlsx
+++ b/Horarios/HorarioWAN_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L00614578\Documents\Github\WAN\Horarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4F5B43-EF6F-46D4-B0CC-AA0BFC17ABFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5E7BC2-C7A3-41F8-87DA-B902D9EA636E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -568,6 +568,69 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -577,15 +640,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -598,9 +652,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -616,94 +667,43 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1983,19 +1983,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="41" t="s">
+      <c r="C3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2022,11 +2022,11 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="30"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
       <c r="I4" s="2" t="s">
         <v>57</v>
       </c>
@@ -2042,11 +2042,11 @@
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="31" t="s">
+      <c r="C5" s="10"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="10" t="s">
         <v>42</v>
       </c>
       <c r="N5" t="s">
@@ -2061,38 +2061,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="31"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="31"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
@@ -2122,19 +2122,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="10" t="s">
         <v>42</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -2152,11 +2152,11 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="31"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="10"/>
       <c r="N13" t="s">
         <v>23</v>
       </c>
@@ -2168,15 +2168,15 @@
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="10" t="s">
+      <c r="D14" s="18"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="29" t="s">
         <v>43</v>
       </c>
       <c r="N14" t="s">
@@ -2191,13 +2191,13 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="39" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="37"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="29"/>
       <c r="N15" t="s">
         <v>24</v>
       </c>
@@ -2209,22 +2209,22 @@
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="26" t="s">
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="37"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="29"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="15"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="18"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.35">
@@ -2260,19 +2260,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -2302,11 +2302,11 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="32"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="22"/>
       <c r="I22" s="2"/>
       <c r="N22" t="s">
         <v>20</v>
@@ -2320,13 +2320,13 @@
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="28" t="s">
+      <c r="C23" s="36"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="32"/>
+      <c r="G23" s="22"/>
       <c r="N23" t="s">
         <v>24</v>
       </c>
@@ -2339,32 +2339,32 @@
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="36"/>
+      <c r="D24" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="32"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="22"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="33"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="23"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.35">
@@ -2400,19 +2400,19 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="21" t="s">
         <v>42</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -2436,11 +2436,11 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="32"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="22"/>
       <c r="N31" t="s">
         <v>20</v>
       </c>
@@ -2453,17 +2453,17 @@
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="34" t="s">
+      <c r="D32" s="41"/>
+      <c r="E32" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="22"/>
       <c r="N32" t="s">
         <v>24</v>
       </c>
@@ -2476,32 +2476,32 @@
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="32"/>
+      <c r="D33" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="32"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="22"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="33"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="23"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="36"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="26"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.35">
@@ -2537,19 +2537,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="38" t="s">
+      <c r="E39" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="21" t="s">
         <v>36</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -2579,11 +2579,11 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="22"/>
       <c r="I40" s="2" t="s">
         <v>58</v>
       </c>
@@ -2598,13 +2598,13 @@
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="28" t="s">
+      <c r="C41" s="32"/>
+      <c r="D41" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="32"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="22"/>
       <c r="I41" s="2" t="s">
         <v>59</v>
       </c>
@@ -2620,11 +2620,11 @@
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="12"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="32"/>
+      <c r="C42" s="33"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="22"/>
       <c r="T42">
         <f>SUM(T3:T39)</f>
         <v>12</v>
@@ -2634,13 +2634,13 @@
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="29"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="33"/>
+      <c r="C43" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="28"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="23"/>
       <c r="O43">
         <f>SUM(O3:O41)</f>
         <v>110</v>
@@ -2650,10 +2650,10 @@
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.35">
@@ -2708,34 +2708,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F17"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="E21:E26"/>
     <mergeCell ref="C21:C26"/>
@@ -2751,9 +2723,37 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="D41:D44"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="54" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="40" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2800,19 +2800,19 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="13" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2820,21 +2820,21 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="30"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="31" t="s">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="10" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2842,38 +2842,38 @@
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="31"/>
+      <c r="F6" s="10"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="31"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="6"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -2903,19 +2903,19 @@
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="10" t="s">
         <v>42</v>
       </c>
     </row>
@@ -2923,23 +2923,23 @@
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="31"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="30" t="s">
+      <c r="C14" s="18"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="13" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2947,36 +2947,36 @@
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="39" t="s">
+      <c r="B15" s="17"/>
+      <c r="C15" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="30"/>
+      <c r="D15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="26" t="s">
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="30"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="27"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="15"/>
       <c r="F17" s="7"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -3006,19 +3006,19 @@
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="E21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="21" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3026,58 +3026,58 @@
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="32"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="22"/>
     </row>
     <row r="23" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="28" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="32"/>
+      <c r="F23" s="22"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="10" t="s">
+      <c r="B24" s="17"/>
+      <c r="C24" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="21"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="32"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="22"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="33"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="23"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="15"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="18"/>
       <c r="F26" s="7"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -3107,19 +3107,19 @@
       <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="21" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3127,58 +3127,58 @@
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="32"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="22"/>
     </row>
     <row r="32" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="43" t="s">
+      <c r="C32" s="41"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="32"/>
+      <c r="F32" s="22"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="10" t="s">
+      <c r="B33" s="32"/>
+      <c r="C33" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="44"/>
-      <c r="F33" s="32"/>
+      <c r="D33" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="55"/>
+      <c r="F33" s="22"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="33"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="23"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="22"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="39"/>
       <c r="F35" s="7"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -3208,19 +3208,19 @@
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="45" t="s">
+      <c r="F39" s="43" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3228,54 +3228,54 @@
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="54"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="52"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="50"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="54"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="52"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="50"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="10" t="s">
+      <c r="B42" s="52"/>
+      <c r="C42" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="32"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="52"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="50"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="53"/>
+      <c r="B43" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="32"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="51"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="47"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="45"/>
       <c r="F44" s="7"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -3305,87 +3305,79 @@
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="45" t="s">
+      <c r="B48" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="46"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="46"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="49"/>
+      <c r="F49" s="49"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="46"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="49"/>
+      <c r="F50" s="49"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="46"/>
-      <c r="C51" s="49"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="49"/>
+      <c r="F51" s="49"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="46"/>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="49"/>
+      <c r="F52" s="49"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="47"/>
-      <c r="C53" s="50"/>
-      <c r="D53" s="50"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="48"/>
+      <c r="D53" s="48"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="F14:F16"/>
     <mergeCell ref="D15:D17"/>
@@ -3402,19 +3394,27 @@
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="E12:E15"/>
     <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="B43:B44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3465,19 +3465,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="41" t="s">
+      <c r="C3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="13" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2"/>
@@ -3486,22 +3486,22 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="30"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="31" t="s">
+      <c r="C5" s="10"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="10" t="s">
         <v>42</v>
       </c>
     </row>
@@ -3509,38 +3509,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="31"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="31"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
+      <c r="C8" s="12"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
@@ -3570,19 +3570,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="10" t="s">
         <v>42</v>
       </c>
       <c r="I12" s="2"/>
@@ -3591,25 +3591,25 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="31"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="10" t="s">
+      <c r="D14" s="18"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="29" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3617,34 +3617,34 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="39" t="s">
+      <c r="C15" s="17"/>
+      <c r="D15" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="37"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="29"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="26" t="s">
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="37"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="29"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="15"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="18"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
@@ -3674,19 +3674,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="26" t="s">
+      <c r="F21" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2"/>
@@ -3695,55 +3695,55 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="32"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="22"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="28" t="s">
+      <c r="C23" s="36"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="32"/>
+      <c r="G23" s="22"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="36"/>
+      <c r="D24" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="32"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="22"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="33"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="23"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
@@ -3773,19 +3773,19 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="D30" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="21" t="s">
         <v>42</v>
       </c>
       <c r="I30" s="2"/>
@@ -3794,58 +3794,58 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="32"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="22"/>
     </row>
     <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="34" t="s">
+      <c r="D32" s="41"/>
+      <c r="E32" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="22"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="32"/>
+      <c r="D33" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="32"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="22"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="33"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="38"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="23"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="36"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="26"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
@@ -3875,19 +3875,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D39" s="26" t="s">
+      <c r="C39" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="38" t="s">
+      <c r="E39" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="21" t="s">
         <v>36</v>
       </c>
       <c r="I39" s="2"/>
@@ -3896,83 +3896,70 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="32"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="22"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="11"/>
-      <c r="D41" s="28" t="s">
+      <c r="C41" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="32"/>
+      <c r="D41" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="22"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="12"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="32"/>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="22"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="29"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="33"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="23"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
       <c r="G44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C39:C42"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="D41:D44"/>
-    <mergeCell ref="C43:C44"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="C32:C35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
     <mergeCell ref="C12:C13"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E15"/>
@@ -3983,16 +3970,29 @@
     <mergeCell ref="G14:G16"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="C32:C35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="D41:D44"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Horarios/HorarioWAN_2025.xlsx
+++ b/Horarios/HorarioWAN_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L00614578\Documents\Github\WAN\Horarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5E7BC2-C7A3-41F8-87DA-B902D9EA636E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C5A125-D2F1-4E35-9343-0F6D53AF6ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
@@ -3878,7 +3878,7 @@
       <c r="C39" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="19" t="s">
         <v>32</v>
       </c>
       <c r="E39" s="21" t="s">
@@ -3897,7 +3897,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="54"/>
-      <c r="D40" s="15"/>
+      <c r="D40" s="42"/>
       <c r="E40" s="17"/>
       <c r="F40" s="17"/>
       <c r="G40" s="22"/>
@@ -3910,9 +3910,7 @@
       <c r="C41" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="27" t="s">
-        <v>33</v>
-      </c>
+      <c r="D41" s="41"/>
       <c r="E41" s="17"/>
       <c r="F41" s="17"/>
       <c r="G41" s="22"/>
@@ -3923,7 +3921,9 @@
         <v>3</v>
       </c>
       <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
+      <c r="D42" s="31" t="s">
+        <v>33</v>
+      </c>
       <c r="E42" s="17"/>
       <c r="F42" s="17"/>
       <c r="G42" s="22"/>
@@ -3933,7 +3933,7 @@
         <v>4</v>
       </c>
       <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
+      <c r="D43" s="32"/>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
       <c r="G43" s="23"/>
@@ -3943,7 +3943,7 @@
         <v>5</v>
       </c>
       <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
+      <c r="D44" s="33"/>
       <c r="E44" s="18"/>
       <c r="F44" s="18"/>
       <c r="G44" s="7"/>
@@ -3977,6 +3977,7 @@
     <mergeCell ref="G21:G25"/>
     <mergeCell ref="F23:F26"/>
     <mergeCell ref="D24:D26"/>
+    <mergeCell ref="G39:G43"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D30:D32"/>
     <mergeCell ref="E30:E31"/>
@@ -3986,13 +3987,12 @@
     <mergeCell ref="E32:E35"/>
     <mergeCell ref="F32:F35"/>
     <mergeCell ref="D33:D35"/>
-    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C44"/>
     <mergeCell ref="E39:E44"/>
     <mergeCell ref="F39:F44"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="D41:D44"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="C41:C44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Horarios/HorarioWAN_2025.xlsx
+++ b/Horarios/HorarioWAN_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L00614578\Documents\Github\WAN\Horarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C5A125-D2F1-4E35-9343-0F6D53AF6ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AC7112-6017-42C2-B0E6-B43CF9EF99A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="73">
   <si>
     <t>3:00 - 4:00</t>
   </si>
@@ -146,87 +146,9 @@
     <t>EXAMEN INTEGRADOR (EVIDENCIA 1)</t>
   </si>
   <si>
-    <t>PRESENTACIÓN DEL RETO CON SOCIO FORMADOR</t>
-  </si>
-  <si>
     <t>PRESENTACIÓN DE LA PROPUESTA DE SOLUCIÓN AL RETO / EVALUACIÓN DEL RETO (EVIDENCIA 2)</t>
   </si>
   <si>
-    <r>
-      <t>SEMANA 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (6 - 10 de Mayo)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SEMANA 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (13 - 17 de Mayo)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SEMANA 3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (20 - 24 de Mayo)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SEMANA 4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (27 - 31 de Mayo)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>SEMANA 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (3 - 7 de Junio)</t>
-    </r>
-  </si>
-  <si>
     <t>AVANCE DEL RETO / RETROALIMENTACIÓN</t>
   </si>
   <si>
@@ -234,21 +156,6 @@
   </si>
   <si>
     <t>PRESENTACIÓN DE PROPUESTA DE SOLUCIÓN AL RETO / EVALUACIÓN DEL RETO (EVIDENCIA 2)</t>
-  </si>
-  <si>
-    <r>
-      <t>SEMANA 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (10 de Junio)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -369,6 +276,120 @@
   </si>
   <si>
     <t>3:00 a 5:30</t>
+  </si>
+  <si>
+    <r>
+      <t>SEMANA 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (5 - 9 de Mayo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SEMANA 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (12 - 16 de Mayo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SEMANA 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (19 - 23 de Mayo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SEMANA 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (26 - 30 de Mayo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SEMANA 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (2 - 6 de Junio)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SEMANA 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (9 de Junio)</t>
+    </r>
+  </si>
+  <si>
+    <t>3:00 a 6:00</t>
+  </si>
+  <si>
+    <t>3:00 a 7:00</t>
+  </si>
+  <si>
+    <t>5:30 - 6:30</t>
+  </si>
+  <si>
+    <t>PRESENTACIÓN DEL RETO CON SOCIO FORMADOR / RETO</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>4 de Junio. Presentación final ante socio formador y coevaluación.</t>
+  </si>
+  <si>
+    <t>23 de Mayo. Presentación ante socio formador.</t>
+  </si>
+  <si>
+    <t>Miércoles 7 de Mayo. Visita CAETEC horario por confirmar</t>
   </si>
 </sst>
 </file>
@@ -568,103 +589,109 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -697,13 +724,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1955,7 +1976,7 @@
   <sheetData>
     <row r="1" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="2:20" x14ac:dyDescent="0.35">
@@ -1976,30 +1997,30 @@
         <v>10</v>
       </c>
       <c r="R2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="30" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="N3" t="s">
         <v>19</v>
@@ -2009,7 +2030,7 @@
         <v>12</v>
       </c>
       <c r="Q3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="R3" t="s">
         <v>0</v>
@@ -2022,13 +2043,13 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="30"/>
       <c r="I4" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="N4" t="s">
         <v>20</v>
@@ -2042,12 +2063,12 @@
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="10" t="s">
-        <v>42</v>
+      <c r="C5" s="31"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="31" t="s">
+        <v>36</v>
       </c>
       <c r="N5" t="s">
         <v>24</v>
@@ -2061,43 +2082,43 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="10"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B10" s="9" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.35">
@@ -2122,23 +2143,23 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>42</v>
+      <c r="G12" s="31" t="s">
+        <v>36</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="N12" t="s">
         <v>19</v>
@@ -2152,11 +2173,11 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="31"/>
       <c r="N13" t="s">
         <v>23</v>
       </c>
@@ -2168,16 +2189,16 @@
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="31" t="s">
+      <c r="D14" s="15"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="29" t="s">
-        <v>43</v>
+      <c r="G14" s="37" t="s">
+        <v>37</v>
       </c>
       <c r="N14" t="s">
         <v>20</v>
@@ -2191,13 +2212,13 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="16" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="29"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="37"/>
       <c r="N15" t="s">
         <v>24</v>
       </c>
@@ -2209,27 +2230,27 @@
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="14" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="29"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="37"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="18"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="15"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B19" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.35">
@@ -2250,33 +2271,33 @@
         <v>10</v>
       </c>
       <c r="R20" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="S20" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" s="14" t="s">
+      <c r="E21" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="13" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="N21" t="s">
         <v>23</v>
@@ -2286,13 +2307,13 @@
         <v>5.5</v>
       </c>
       <c r="Q21" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="R21" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="S21" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="T21">
         <v>4.5</v>
@@ -2302,11 +2323,11 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="22"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="32"/>
       <c r="I22" s="2"/>
       <c r="N22" t="s">
         <v>20</v>
@@ -2320,13 +2341,13 @@
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="27" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="22"/>
+      <c r="G23" s="32"/>
       <c r="N23" t="s">
         <v>24</v>
       </c>
@@ -2339,37 +2360,37 @@
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="31" t="s">
+      <c r="C24" s="18"/>
+      <c r="D24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="22"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="32"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="23"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="33"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B28" s="9" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.35">
@@ -2390,7 +2411,7 @@
         <v>10</v>
       </c>
       <c r="R29" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="T29">
         <v>2</v>
@@ -2400,23 +2421,23 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="21" t="s">
-        <v>42</v>
+      <c r="G30" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="N30" t="s">
         <v>23</v>
@@ -2426,21 +2447,21 @@
         <v>10.5</v>
       </c>
       <c r="Q30" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="R30" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="22"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="32"/>
       <c r="N31" t="s">
         <v>20</v>
       </c>
@@ -2453,17 +2474,17 @@
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="24" t="s">
+      <c r="D32" s="24"/>
+      <c r="E32" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="22"/>
+      <c r="G32" s="32"/>
       <c r="N32" t="s">
         <v>24</v>
       </c>
@@ -2476,37 +2497,37 @@
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="31" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="22"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="32"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="23"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="33"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="26"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B37" s="9" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.35">
@@ -2527,33 +2548,33 @@
         <v>10</v>
       </c>
       <c r="R38" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="S38" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="2:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="D39" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="30" t="s">
+      <c r="E39" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="21" t="s">
-        <v>36</v>
+      <c r="G39" s="13" t="s">
+        <v>35</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="N39" t="s">
         <v>23</v>
@@ -2563,13 +2584,13 @@
         <v>6</v>
       </c>
       <c r="Q39" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="R39" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="S39" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="T39">
         <v>4.5</v>
@@ -2579,13 +2600,13 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="32"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="32"/>
       <c r="I40" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="N40" t="s">
         <v>20</v>
@@ -2598,15 +2619,15 @@
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="32"/>
-      <c r="D41" s="27" t="s">
+      <c r="C41" s="11"/>
+      <c r="D41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="22"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="32"/>
       <c r="I41" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="N41" t="s">
         <v>24</v>
@@ -2620,11 +2641,11 @@
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="22"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="32"/>
       <c r="T42">
         <f>SUM(T3:T39)</f>
         <v>12</v>
@@ -2634,13 +2655,13 @@
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="28"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="23"/>
+      <c r="C43" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="29"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="33"/>
       <c r="O43">
         <f>SUM(O3:O41)</f>
         <v>110</v>
@@ -2650,10 +2671,10 @@
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="40"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.35">
@@ -2708,6 +2729,34 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F17"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="E21:E26"/>
     <mergeCell ref="C21:C26"/>
@@ -2723,34 +2772,6 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="D41:D44"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="40" orientation="portrait" r:id="rId1"/>
@@ -2762,7 +2783,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" style="3"/>
@@ -2770,15 +2791,17 @@
     <col min="3" max="3" width="15.1796875" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.36328125" style="3" customWidth="1"/>
     <col min="5" max="5" width="13" style="3" customWidth="1"/>
-    <col min="6" max="6" width="19.453125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.08984375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.6328125" customWidth="1"/>
+    <col min="8" max="8" width="67.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
         <v>6</v>
@@ -2795,93 +2818,119 @@
       <c r="F2" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="I3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="N3" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="13"/>
-    </row>
-    <row r="5" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="23"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="30"/>
+      <c r="L4" t="s">
+        <v>69</v>
+      </c>
+      <c r="N4" s="40"/>
+    </row>
+    <row r="5" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B5" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="40"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="31"/>
+      <c r="H5" t="s">
+        <v>72</v>
+      </c>
+      <c r="N5" s="40"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="13" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="31"/>
+      <c r="N6" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="10"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="10"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B7" s="42"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="31"/>
+      <c r="N7" s="40"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="40"/>
       <c r="F8" s="6"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="N8" s="40"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="4" t="s">
         <v>6</v>
@@ -2899,92 +2948,92 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F12" s="31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="10"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B13" s="27"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="31"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C14" s="15"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="30" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="16" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D15" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="42"/>
+      <c r="F15" s="30"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="14" t="s">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F16" s="30"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="27"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="4" t="s">
         <v>6</v>
@@ -3001,91 +3050,112 @@
       <c r="F20" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J20" t="s">
+        <v>55</v>
+      </c>
+      <c r="K20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F21" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" t="s">
+        <v>71</v>
+      </c>
+      <c r="I21" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" t="s">
+        <v>65</v>
+      </c>
+      <c r="K21" t="s">
+        <v>56</v>
+      </c>
+      <c r="L21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="22"/>
-    </row>
-    <row r="23" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="27"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="32"/>
+    </row>
+    <row r="23" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="27" t="s">
+      <c r="C23" s="15"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="22"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F23" s="32"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="31" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="22"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D24" s="23"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="32"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="23"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B25" s="14"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="29"/>
+      <c r="F25" s="33"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="18"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="15"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="4" t="s">
         <v>6</v>
@@ -3102,91 +3172,109 @@
       <c r="F29" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J29" t="s">
+        <v>55</v>
+      </c>
+      <c r="K29" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="D30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F30" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" t="s">
+        <v>67</v>
+      </c>
+      <c r="K30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="42"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="22"/>
-    </row>
-    <row r="32" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="24"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="32"/>
+    </row>
+    <row r="32" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="41"/>
-      <c r="D32" s="40"/>
-      <c r="E32" s="53" t="s">
+      <c r="C32" s="24"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="22"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F32" s="32"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="32"/>
-      <c r="C33" s="31" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="55"/>
-      <c r="F33" s="22"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D33" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="44"/>
+      <c r="F33" s="32"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="55"/>
-      <c r="F34" s="23"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="33"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="33"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="39"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="22"/>
       <c r="F35" s="7"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="4" t="s">
         <v>6</v>
@@ -3203,87 +3291,105 @@
       <c r="F38" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J38" t="s">
+        <v>55</v>
+      </c>
+      <c r="K38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="31" t="s">
+      <c r="B39" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="43" t="s">
+      <c r="D39" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="43" t="s">
+      <c r="F39" s="45" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H39" t="s">
+        <v>70</v>
+      </c>
+      <c r="I39" t="s">
+        <v>53</v>
+      </c>
+      <c r="J39" t="s">
+        <v>56</v>
+      </c>
+      <c r="K39" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="52"/>
-      <c r="C40" s="42"/>
-      <c r="D40" s="22"/>
-      <c r="E40" s="44"/>
-      <c r="F40" s="50"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B40" s="54"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="52"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="52"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="50"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B41" s="54"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="46"/>
+      <c r="F41" s="52"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="52"/>
-      <c r="C42" s="31" t="s">
+      <c r="B42" s="54"/>
+      <c r="C42" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="22"/>
-      <c r="E42" s="44"/>
-      <c r="F42" s="50"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D42" s="32"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="52"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="32"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="51"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B43" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="11"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="53"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="54"/>
-      <c r="C44" s="33"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="45"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="33"/>
+      <c r="E44" s="47"/>
       <c r="F44" s="7"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="4" t="s">
         <v>6</v>
@@ -3301,108 +3407,78 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="43" t="s">
+      <c r="B48" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="46"/>
-      <c r="F48" s="46"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="48"/>
+      <c r="E48" s="48"/>
+      <c r="F48" s="48"/>
+      <c r="L48">
+        <f>SUM(L3+L21+L29)</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="44"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="49"/>
-      <c r="F49" s="49"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="49"/>
+      <c r="E49" s="51"/>
+      <c r="F49" s="51"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="44"/>
-      <c r="C50" s="47"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="49"/>
-      <c r="F50" s="49"/>
+      <c r="B50" s="46"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="49"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="44"/>
-      <c r="C51" s="47"/>
-      <c r="D51" s="47"/>
-      <c r="E51" s="49"/>
-      <c r="F51" s="49"/>
+      <c r="B51" s="46"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="49"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="44"/>
-      <c r="C52" s="47"/>
-      <c r="D52" s="47"/>
-      <c r="E52" s="49"/>
-      <c r="F52" s="49"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="49"/>
+      <c r="E52" s="51"/>
+      <c r="F52" s="51"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="45"/>
-      <c r="C53" s="48"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26"/>
+      <c r="B53" s="47"/>
+      <c r="C53" s="50"/>
+      <c r="D53" s="50"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="E30:E31"/>
+  <mergeCells count="52">
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="N6:N8"/>
     <mergeCell ref="D39:D44"/>
     <mergeCell ref="E39:E44"/>
     <mergeCell ref="B48:B53"/>
@@ -3415,6 +3491,42 @@
     <mergeCell ref="E48:E53"/>
     <mergeCell ref="B39:B42"/>
     <mergeCell ref="B43:B44"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3440,7 +3552,7 @@
   <sheetData>
     <row r="1" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B1" s="9" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.35">
@@ -3465,19 +3577,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="30" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2"/>
@@ -3486,66 +3598,66 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="13"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="30"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="10" t="s">
-        <v>42</v>
+      <c r="C5" s="31"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="31" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="10"/>
+      <c r="G6" s="31"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="10"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="31"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B10" s="9" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.35">
@@ -3570,20 +3682,20 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>42</v>
+      <c r="G12" s="31" t="s">
+        <v>36</v>
       </c>
       <c r="I12" s="2"/>
     </row>
@@ -3591,65 +3703,65 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="10"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="31"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="31" t="s">
+      <c r="D14" s="15"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="29" t="s">
-        <v>43</v>
+      <c r="G14" s="37" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="16" t="s">
+      <c r="C15" s="14"/>
+      <c r="D15" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="29"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="37"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="14" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="17"/>
-      <c r="G16" s="29"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="37"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="18"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="15"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B19" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.35">
@@ -3674,19 +3786,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="34" t="s">
+      <c r="C21" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" s="14" t="s">
+      <c r="E21" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="13" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2"/>
@@ -3695,60 +3807,60 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="22"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="32"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="36"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="27" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="22"/>
+      <c r="G23" s="32"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="31" t="s">
+      <c r="C24" s="18"/>
+      <c r="D24" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="22"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="32"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="36"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="23"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="33"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B28" s="9" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.35">
@@ -3773,20 +3885,20 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="14" t="s">
+      <c r="F30" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G30" s="21" t="s">
-        <v>42</v>
+      <c r="G30" s="13" t="s">
+        <v>36</v>
       </c>
       <c r="I30" s="2"/>
     </row>
@@ -3794,63 +3906,63 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="41"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="22"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="32"/>
     </row>
     <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="24" t="s">
+      <c r="D32" s="24"/>
+      <c r="E32" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="22"/>
+      <c r="G32" s="32"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="31" t="s">
+      <c r="C33" s="11"/>
+      <c r="D33" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="22"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="32"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="23"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="33"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="26"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="36"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B37" s="9" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.35">
@@ -3875,20 +3987,20 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="19" t="s">
+      <c r="C39" s="43" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="30" t="s">
+      <c r="E39" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="21" t="s">
-        <v>36</v>
+      <c r="G39" s="13" t="s">
+        <v>35</v>
       </c>
       <c r="I39" s="2"/>
     </row>
@@ -3896,87 +4008,60 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="54"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="22"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="32"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="41"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="22"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="32"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="28"/>
-      <c r="D42" s="31" t="s">
+      <c r="C42" s="29"/>
+      <c r="D42" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="22"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="32"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="28"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="23"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="33"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
       <c r="G44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
     <mergeCell ref="G39:G43"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D30:D32"/>
@@ -3993,6 +4078,33 @@
     <mergeCell ref="C41:C44"/>
     <mergeCell ref="E39:E44"/>
     <mergeCell ref="F39:F44"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Horarios/HorarioWAN_2025.xlsx
+++ b/Horarios/HorarioWAN_2025.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L00614578\Documents\Github\WAN\Horarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1AC7112-6017-42C2-B0E6-B43CF9EF99A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F509EEDC-4333-4E9C-A334-F4E95A33652B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" activeTab="4" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
     <sheet name="WAN_201" sheetId="2" r:id="rId2"/>
     <sheet name="WAN_301" sheetId="4" r:id="rId3"/>
     <sheet name="WAN_201_Canvas" sheetId="5" r:id="rId4"/>
+    <sheet name="WAN_301_Canvas" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="73">
   <si>
     <t>3:00 - 4:00</t>
   </si>
@@ -564,7 +565,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -589,6 +590,72 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -598,15 +665,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -619,9 +677,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -637,94 +692,43 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2004,19 +2008,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="30" t="s">
+      <c r="C3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="30" t="s">
+      <c r="F3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2043,11 +2047,11 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="30"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="14"/>
       <c r="I4" s="2" t="s">
         <v>50</v>
       </c>
@@ -2063,11 +2067,11 @@
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="31" t="s">
+      <c r="C5" s="11"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="11" t="s">
         <v>36</v>
       </c>
       <c r="N5" t="s">
@@ -2082,38 +2086,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="30" t="s">
+      <c r="E6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="31"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="31"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
@@ -2143,19 +2147,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="15" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="31" t="s">
+      <c r="F12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -2173,11 +2177,11 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="31"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="11"/>
       <c r="N13" t="s">
         <v>23</v>
       </c>
@@ -2189,15 +2193,15 @@
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="10" t="s">
+      <c r="D14" s="19"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="30" t="s">
         <v>37</v>
       </c>
       <c r="N14" t="s">
@@ -2212,13 +2216,13 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="39" t="s">
+      <c r="C15" s="18"/>
+      <c r="D15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="37"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="30"/>
       <c r="N15" t="s">
         <v>24</v>
       </c>
@@ -2230,22 +2234,22 @@
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="37"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="30"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="15"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.35">
@@ -2281,19 +2285,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="35" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="13" t="s">
+      <c r="F21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -2323,11 +2327,11 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="32"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="23"/>
       <c r="I22" s="2"/>
       <c r="N22" t="s">
         <v>20</v>
@@ -2341,13 +2345,13 @@
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="14"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="32"/>
+      <c r="G23" s="23"/>
       <c r="N23" t="s">
         <v>24</v>
       </c>
@@ -2360,32 +2364,32 @@
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="37"/>
+      <c r="D24" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="14"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="29"/>
-      <c r="G24" s="32"/>
+      <c r="G24" s="23"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="14"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="29"/>
-      <c r="G25" s="33"/>
+      <c r="G25" s="24"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.35">
@@ -2427,13 +2431,13 @@
       <c r="D30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="13" t="s">
+      <c r="F30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>36</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -2457,11 +2461,11 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="32"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="23"/>
       <c r="N31" t="s">
         <v>20</v>
       </c>
@@ -2474,17 +2478,17 @@
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="34" t="s">
+      <c r="D32" s="42"/>
+      <c r="E32" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="23"/>
       <c r="N32" t="s">
         <v>24</v>
       </c>
@@ -2497,32 +2501,32 @@
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="33"/>
+      <c r="D33" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="32"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="23"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="24"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="36"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="27"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.35">
@@ -2558,19 +2562,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="38" t="s">
+      <c r="D39" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -2600,11 +2604,11 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="32"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="23"/>
       <c r="I40" s="2" t="s">
         <v>51</v>
       </c>
@@ -2619,13 +2623,13 @@
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="11"/>
+      <c r="C41" s="33"/>
       <c r="D41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="32"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="23"/>
       <c r="I41" s="2" t="s">
         <v>52</v>
       </c>
@@ -2641,11 +2645,11 @@
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="12"/>
+      <c r="C42" s="34"/>
       <c r="D42" s="29"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="32"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="23"/>
       <c r="T42">
         <f>SUM(T3:T39)</f>
         <v>12</v>
@@ -2655,13 +2659,13 @@
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="22" t="s">
         <v>22</v>
       </c>
       <c r="D43" s="29"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="33"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="24"/>
       <c r="O43">
         <f>SUM(O3:O41)</f>
         <v>110</v>
@@ -2671,10 +2675,10 @@
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.35">
@@ -2729,34 +2733,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F17"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="E21:E26"/>
     <mergeCell ref="C21:C26"/>
@@ -2772,6 +2748,34 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="D41:D44"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="40" orientation="portrait" r:id="rId1"/>
@@ -2826,19 +2830,19 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="30" t="s">
+      <c r="B3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I3" t="s">
@@ -2850,7 +2854,7 @@
       <c r="L3">
         <v>1</v>
       </c>
-      <c r="N3" s="30" t="s">
+      <c r="N3" s="14" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2858,48 +2862,48 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="30"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14"/>
       <c r="L4" t="s">
         <v>69</v>
       </c>
-      <c r="N4" s="40"/>
+      <c r="N4" s="13"/>
     </row>
     <row r="5" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="31"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="22" t="s">
+        <v>22</v>
+      </c>
       <c r="H5" t="s">
         <v>72</v>
       </c>
-      <c r="N5" s="40"/>
+      <c r="N5" s="13"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="30" t="s">
+      <c r="D6" s="21"/>
+      <c r="E6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="31"/>
-      <c r="N6" s="41" t="s">
+      <c r="F6" s="21"/>
+      <c r="N6" s="12" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2907,23 +2911,25 @@
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="31"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="31"/>
-      <c r="N7" s="40"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="B7" s="21"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="41"/>
+      <c r="N7" s="13"/>
+    </row>
+    <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="40"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="13"/>
       <c r="F8" s="6"/>
-      <c r="N8" s="40"/>
+      <c r="N8" s="13"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
@@ -2952,19 +2958,19 @@
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="15" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="31" t="s">
+      <c r="F12" s="11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2972,23 +2978,23 @@
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="31"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="30" t="s">
+      <c r="C14" s="19"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="14" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2996,36 +3002,36 @@
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="39" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="30"/>
+      <c r="D15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="30"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="14"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="27"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="7"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -3061,19 +3067,19 @@
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="15" t="s">
         <v>32</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="13" t="s">
+      <c r="D21" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="22" t="s">
         <v>68</v>
       </c>
       <c r="H21" t="s">
@@ -3096,58 +3102,58 @@
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="27"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="32"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="23"/>
     </row>
     <row r="23" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="42"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="21"/>
       <c r="E23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="32"/>
+      <c r="F23" s="23"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="10" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="23"/>
+      <c r="D24" s="41"/>
       <c r="E24" s="29"/>
-      <c r="F24" s="32"/>
+      <c r="F24" s="23"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="26" t="s">
+      <c r="B25" s="18"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="15" t="s">
         <v>32</v>
       </c>
       <c r="E25" s="29"/>
-      <c r="F25" s="33"/>
+      <c r="F25" s="24"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="15"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="19"/>
       <c r="F26" s="7"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
@@ -3192,13 +3198,13 @@
       <c r="C30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="13" t="s">
+      <c r="E30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="22" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
@@ -3215,58 +3221,58 @@
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="32"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="23"/>
     </row>
     <row r="32" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="24"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="43" t="s">
+      <c r="C32" s="42"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="32"/>
+      <c r="F32" s="23"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="11"/>
-      <c r="C33" s="10" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="44"/>
-      <c r="F33" s="32"/>
+      <c r="D33" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="56"/>
+      <c r="F33" s="23"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="33"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="24"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="22"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="40"/>
       <c r="F35" s="7"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
@@ -3302,19 +3308,19 @@
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="32" t="s">
         <v>33</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="45" t="s">
+      <c r="F39" s="44" t="s">
         <v>26</v>
       </c>
       <c r="H39" t="s">
@@ -3334,54 +3340,54 @@
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="54"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="52"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="51"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="54"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="46"/>
-      <c r="F41" s="52"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="51"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="54"/>
-      <c r="C42" s="10" t="s">
+      <c r="B42" s="53"/>
+      <c r="C42" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="32"/>
-      <c r="E42" s="46"/>
-      <c r="F42" s="52"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="51"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="53"/>
+      <c r="B43" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="33"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="52"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B44" s="55"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="33"/>
-      <c r="E44" s="47"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="46"/>
       <c r="F44" s="7"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
@@ -3411,13 +3417,13 @@
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="45" t="s">
+      <c r="B48" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
       <c r="L48">
         <f>SUM(L3+L21+L29)</f>
         <v>11</v>
@@ -3427,60 +3433,85 @@
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="46"/>
-      <c r="C49" s="49"/>
-      <c r="D49" s="49"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="46"/>
-      <c r="C50" s="49"/>
-      <c r="D50" s="49"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="48"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="46"/>
-      <c r="C51" s="49"/>
-      <c r="D51" s="49"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="46"/>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="48"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="47"/>
-      <c r="C53" s="50"/>
-      <c r="D53" s="50"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
+      <c r="B53" s="46"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="51">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="C24:C26"/>
     <mergeCell ref="D21:D24"/>
     <mergeCell ref="D25:D26"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E30:E31"/>
     <mergeCell ref="B48:B53"/>
     <mergeCell ref="C48:C53"/>
     <mergeCell ref="F48:F53"/>
@@ -3491,42 +3522,16 @@
     <mergeCell ref="E48:E53"/>
     <mergeCell ref="B39:B42"/>
     <mergeCell ref="B43:B44"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="E39:E44"/>
     <mergeCell ref="F30:F34"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="E30:E31"/>
     <mergeCell ref="F12:F13"/>
     <mergeCell ref="F14:F16"/>
     <mergeCell ref="D15:D17"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B5:B8"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3577,19 +3582,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="30" t="s">
+      <c r="C3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="30" t="s">
+      <c r="F3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2"/>
@@ -3598,22 +3603,22 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="30"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="14"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="31" t="s">
+      <c r="C5" s="11"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3621,38 +3626,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="30" t="s">
+      <c r="E6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="31"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="31"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
@@ -3682,19 +3687,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="15" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="31" t="s">
+      <c r="F12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="2"/>
@@ -3703,25 +3708,25 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="31"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="10" t="s">
+      <c r="D14" s="19"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="30" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3729,34 +3734,34 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="39" t="s">
+      <c r="C15" s="18"/>
+      <c r="D15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="37"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="30"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="37"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="30"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="15"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
@@ -3786,19 +3791,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="35" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="13" t="s">
+      <c r="F21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2"/>
@@ -3807,55 +3812,55 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="32"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="23"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="14"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="18"/>
       <c r="F23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="32"/>
+      <c r="G23" s="23"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="37"/>
+      <c r="D24" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="14"/>
+      <c r="E24" s="18"/>
       <c r="F24" s="29"/>
-      <c r="G24" s="32"/>
+      <c r="G24" s="23"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="14"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="29"/>
-      <c r="G25" s="33"/>
+      <c r="G25" s="24"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
@@ -3891,13 +3896,13 @@
       <c r="D30" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="13" t="s">
+      <c r="F30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>36</v>
       </c>
       <c r="I30" s="2"/>
@@ -3906,58 +3911,58 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="32"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="24"/>
-      <c r="E32" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="34" t="s">
+      <c r="D32" s="42"/>
+      <c r="E32" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="23"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="10" t="s">
+      <c r="C33" s="33"/>
+      <c r="D33" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="35"/>
-      <c r="G33" s="32"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="23"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="24"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="36"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="27"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
@@ -3987,19 +3992,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="43" t="s">
+      <c r="C39" s="54" t="s">
         <v>22</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="E39" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="38" t="s">
+      <c r="E39" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I39" s="2"/>
@@ -4009,10 +4014,10 @@
         <v>1</v>
       </c>
       <c r="C40" s="55"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="32"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="23"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
@@ -4022,10 +4027,10 @@
       <c r="C41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="32"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="23"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
@@ -4033,35 +4038,62 @@
         <v>3</v>
       </c>
       <c r="C42" s="29"/>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="32"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="23"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C43" s="29"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="24"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="15"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
       <c r="G44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
     <mergeCell ref="G39:G43"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D30:D32"/>
@@ -4078,35 +4110,672 @@
     <mergeCell ref="C41:C44"/>
     <mergeCell ref="E39:E44"/>
     <mergeCell ref="F39:F44"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DDF4198-051C-4816-909A-A01DB9C8A9AE}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F53"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.90625" style="3"/>
+    <col min="2" max="2" width="12.6328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="15.1796875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.36328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.08984375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="5"/>
+      <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14"/>
+    </row>
+    <row r="5" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21"/>
+      <c r="C6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="21"/>
+      <c r="E6" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="21"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="41"/>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="13"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="5"/>
+      <c r="B11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="5"/>
+      <c r="B20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="23"/>
+    </row>
+    <row r="23" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" s="18"/>
+      <c r="C24" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="41"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="23"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="18"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="29"/>
+      <c r="F25" s="24"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="5"/>
+      <c r="B29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" s="42"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="23"/>
+    </row>
+    <row r="32" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="42"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="23"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="33"/>
+      <c r="C33" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="56"/>
+      <c r="F33" s="23"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="24"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="7"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="5"/>
+      <c r="B38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" s="44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" s="53"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="51"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" s="53"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="51"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="53"/>
+      <c r="C42" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="23"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="51"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="33"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="52"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="55"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="46"/>
+      <c r="F44" s="7"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="5"/>
+      <c r="B47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49" s="45"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="45"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="48"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" s="45"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B52" s="45"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="48"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="46"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="49">
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F4"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="88" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Horarios/HorarioWAN_2025.xlsx
+++ b/Horarios/HorarioWAN_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L00614578\Documents\Github\WAN\Horarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F509EEDC-4333-4E9C-A334-F4E95A33652B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39407BD-C2D2-4C48-BEE3-65224C35A173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" activeTab="4" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="75">
   <si>
     <t>3:00 - 4:00</t>
   </si>
@@ -391,6 +391,12 @@
   </si>
   <si>
     <t>Miércoles 7 de Mayo. Visita CAETEC horario por confirmar</t>
+  </si>
+  <si>
+    <t>3:00 - 7:00 p.m.</t>
+  </si>
+  <si>
+    <t>4:00 a 6:00</t>
   </si>
 </sst>
 </file>
@@ -593,103 +599,109 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -722,13 +734,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2008,19 +2014,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="C3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="31" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2047,11 +2053,11 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="31"/>
       <c r="I4" s="2" t="s">
         <v>50</v>
       </c>
@@ -2067,11 +2073,11 @@
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="11" t="s">
+      <c r="C5" s="32"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="32" t="s">
         <v>36</v>
       </c>
       <c r="N5" t="s">
@@ -2086,38 +2092,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="14" t="s">
+      <c r="E6" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="11"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="32"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
@@ -2147,19 +2153,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="C12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="11" t="s">
+      <c r="F12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="32" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -2177,11 +2183,11 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="11"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="32"/>
       <c r="N13" t="s">
         <v>23</v>
       </c>
@@ -2193,15 +2199,15 @@
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="32" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N14" t="s">
@@ -2216,13 +2222,13 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="17" t="s">
+      <c r="C15" s="15"/>
+      <c r="D15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="30"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="38"/>
       <c r="N15" t="s">
         <v>24</v>
       </c>
@@ -2234,22 +2240,22 @@
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="30"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="38"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="19"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="16"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.35">
@@ -2285,19 +2291,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="22" t="s">
+      <c r="D21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="22" t="s">
+      <c r="F21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -2327,11 +2333,11 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="33"/>
       <c r="I22" s="2"/>
       <c r="N22" t="s">
         <v>20</v>
@@ -2345,13 +2351,13 @@
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="28" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="33"/>
       <c r="N23" t="s">
         <v>24</v>
       </c>
@@ -2364,32 +2370,32 @@
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="19"/>
+      <c r="D24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="23"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="33"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="24"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="34"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.35">
@@ -2425,19 +2431,19 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="32" t="s">
+      <c r="C30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="22" t="s">
+      <c r="F30" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -2461,11 +2467,11 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="23"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="33"/>
       <c r="N31" t="s">
         <v>20</v>
       </c>
@@ -2478,17 +2484,17 @@
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="42"/>
-      <c r="E32" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="25" t="s">
+      <c r="D32" s="25"/>
+      <c r="E32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="23"/>
+      <c r="G32" s="33"/>
       <c r="N32" t="s">
         <v>24</v>
       </c>
@@ -2501,32 +2507,32 @@
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="32" t="s">
+      <c r="C33" s="12"/>
+      <c r="D33" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="23"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="33"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="24"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="34"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="27"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="37"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.35">
@@ -2562,19 +2568,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="31" t="s">
+      <c r="D39" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -2604,11 +2610,11 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="23"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="33"/>
       <c r="I40" s="2" t="s">
         <v>51</v>
       </c>
@@ -2623,13 +2629,13 @@
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="33"/>
-      <c r="D41" s="28" t="s">
+      <c r="C41" s="12"/>
+      <c r="D41" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="23"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="33"/>
       <c r="I41" s="2" t="s">
         <v>52</v>
       </c>
@@ -2645,11 +2651,11 @@
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="23"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="33"/>
       <c r="T42">
         <f>SUM(T3:T39)</f>
         <v>12</v>
@@ -2659,13 +2665,13 @@
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="29"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="24"/>
+      <c r="C43" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="30"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="34"/>
       <c r="O43">
         <f>SUM(O3:O41)</f>
         <v>110</v>
@@ -2675,10 +2681,10 @@
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="41"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.35">
@@ -2733,6 +2739,34 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F17"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="E21:E26"/>
     <mergeCell ref="C21:C26"/>
@@ -2748,34 +2782,6 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="D41:D44"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="40" orientation="portrait" r:id="rId1"/>
@@ -2830,19 +2836,19 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="B3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="31" t="s">
         <v>31</v>
       </c>
       <c r="I3" t="s">
@@ -2854,7 +2860,7 @@
       <c r="L3">
         <v>1</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="N3" s="31" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2862,48 +2868,57 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="31"/>
       <c r="L4" t="s">
         <v>69</v>
       </c>
-      <c r="N4" s="13"/>
+      <c r="N4" s="41"/>
     </row>
     <row r="5" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="22" t="s">
+      <c r="C5" s="41"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="H5" t="s">
         <v>72</v>
       </c>
-      <c r="N5" s="13"/>
+      <c r="J5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" s="41"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="14" t="s">
+      <c r="D6" s="43"/>
+      <c r="E6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="N6" s="12" t="s">
+      <c r="F6" s="43"/>
+      <c r="J6" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6">
+        <v>4</v>
+      </c>
+      <c r="N6" s="42" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2911,25 +2926,25 @@
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="41"/>
-      <c r="N7" s="13"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="24"/>
+      <c r="N7" s="41"/>
     </row>
     <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="13"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="41"/>
       <c r="F8" s="6"/>
-      <c r="N8" s="13"/>
+      <c r="N8" s="41"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
@@ -2958,19 +2973,19 @@
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="14" t="s">
+      <c r="B12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="32" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2978,23 +2993,23 @@
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="11"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="32"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="14" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3002,36 +3017,36 @@
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="14"/>
+      <c r="D15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="31"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="31"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="28"/>
       <c r="F17" s="7"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -3067,19 +3082,19 @@
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="22" t="s">
+      <c r="B21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>68</v>
       </c>
       <c r="H21" t="s">
@@ -3092,7 +3107,7 @@
         <v>65</v>
       </c>
       <c r="K21" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -3102,58 +3117,58 @@
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="23"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="33"/>
     </row>
     <row r="23" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="28" t="s">
+      <c r="C23" s="16"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="23"/>
+      <c r="F23" s="33"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="32" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="33"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="24"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="30"/>
+      <c r="F25" s="34"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="19"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="7"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
@@ -3192,19 +3207,19 @@
       <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="32" t="s">
+      <c r="B30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="22" t="s">
+      <c r="E30" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
@@ -3221,58 +3236,58 @@
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="23"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="33"/>
     </row>
     <row r="32" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="54" t="s">
+      <c r="C32" s="25"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="23"/>
+      <c r="F32" s="33"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="12"/>
+      <c r="C33" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="56"/>
-      <c r="F33" s="23"/>
+      <c r="D33" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="45"/>
+      <c r="F33" s="33"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="24"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="34"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="40"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="23"/>
       <c r="F35" s="7"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
@@ -3308,19 +3323,19 @@
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="22" t="s">
+      <c r="C39" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="44" t="s">
+      <c r="F39" s="46" t="s">
         <v>26</v>
       </c>
       <c r="H39" t="s">
@@ -3340,54 +3355,54 @@
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="53"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="51"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="53"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="53"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="51"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="53"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="53"/>
-      <c r="C42" s="32" t="s">
+      <c r="B42" s="55"/>
+      <c r="C42" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="51"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="53"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="52"/>
+      <c r="B43" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="54"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="46"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="48"/>
       <c r="F44" s="7"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
@@ -3417,101 +3432,80 @@
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="44" t="s">
+      <c r="B48" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
       <c r="L48">
-        <f>SUM(L3+L21+L29)</f>
-        <v>11</v>
+        <f>SUM(L3:L39)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="45"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="50"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="50"/>
-      <c r="F51" s="50"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="45"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="50"/>
-      <c r="F52" s="50"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="46"/>
-      <c r="C53" s="49"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F7"/>
     <mergeCell ref="B48:B53"/>
     <mergeCell ref="C48:C53"/>
     <mergeCell ref="F48:F53"/>
@@ -3522,16 +3516,37 @@
     <mergeCell ref="E48:E53"/>
     <mergeCell ref="B39:B42"/>
     <mergeCell ref="B43:B44"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D3:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3582,19 +3597,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="C3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="31" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2"/>
@@ -3603,22 +3618,22 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="31"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="11" t="s">
+      <c r="C5" s="32"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="32" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3626,38 +3641,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="14" t="s">
+      <c r="E6" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="11"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="32"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
@@ -3687,19 +3702,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="C12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="11" t="s">
+      <c r="F12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="32" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="2"/>
@@ -3708,25 +3723,25 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="11"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="32"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="32" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="38" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3734,34 +3749,34 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="17" t="s">
+      <c r="C15" s="15"/>
+      <c r="D15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="30"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="38"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="30"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="38"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="19"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="16"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
@@ -3791,19 +3806,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="22" t="s">
+      <c r="D21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="22" t="s">
+      <c r="F21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2"/>
@@ -3812,55 +3827,55 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="33"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="28" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="33"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="19"/>
+      <c r="D24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="23"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="33"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="24"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="34"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
@@ -3890,19 +3905,19 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="32" t="s">
+      <c r="C30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="22" t="s">
+      <c r="F30" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I30" s="2"/>
@@ -3911,58 +3926,58 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="23"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="33"/>
     </row>
     <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="42"/>
-      <c r="E32" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="25" t="s">
+      <c r="D32" s="25"/>
+      <c r="E32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="23"/>
+      <c r="G32" s="33"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="32" t="s">
+      <c r="C33" s="12"/>
+      <c r="D33" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="23"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="33"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="24"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="34"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="27"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="37"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
@@ -3992,19 +4007,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="31" t="s">
+      <c r="C39" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I39" s="2"/>
@@ -4013,87 +4028,60 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="23"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="33"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C41" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="42"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="23"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="33"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="29"/>
-      <c r="D42" s="32" t="s">
+      <c r="C42" s="30"/>
+      <c r="D42" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="23"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="33"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="24"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="34"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
       <c r="G44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
     <mergeCell ref="G39:G43"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D30:D32"/>
@@ -4110,6 +4098,33 @@
     <mergeCell ref="C41:C44"/>
     <mergeCell ref="E39:E44"/>
     <mergeCell ref="F39:F44"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4160,19 +4175,19 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="B3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="31" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4180,23 +4195,23 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="31"/>
     </row>
     <row r="5" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="22" t="s">
+      <c r="C5" s="41"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4204,36 +4219,36 @@
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="14" t="s">
+      <c r="D6" s="43"/>
+      <c r="E6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="21"/>
+      <c r="F6" s="43"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="41"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="24"/>
     </row>
     <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="13"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="41"/>
       <c r="F8" s="6"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -4263,19 +4278,19 @@
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="14" t="s">
+      <c r="B12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="32" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4283,23 +4298,23 @@
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="11"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="32"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="14" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4307,36 +4322,36 @@
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="14"/>
+      <c r="D15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="43"/>
+      <c r="F15" s="31"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="31"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="28"/>
       <c r="F17" s="7"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -4366,19 +4381,19 @@
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="22" t="s">
+      <c r="B21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4386,58 +4401,58 @@
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="23"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="33"/>
     </row>
     <row r="23" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="28" t="s">
+      <c r="C23" s="16"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="23"/>
+      <c r="F23" s="33"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="32" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="33"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="24"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="30"/>
+      <c r="F25" s="34"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="19"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="7"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -4467,19 +4482,19 @@
       <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="32" t="s">
+      <c r="B30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="22" t="s">
+      <c r="E30" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="14" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4487,58 +4502,58 @@
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="23"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="33"/>
     </row>
     <row r="32" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="54" t="s">
+      <c r="C32" s="25"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="23"/>
+      <c r="F32" s="33"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="12"/>
+      <c r="C33" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="56"/>
-      <c r="F33" s="23"/>
+      <c r="D33" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="45"/>
+      <c r="F33" s="33"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="24"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="34"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="40"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="23"/>
       <c r="F35" s="7"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -4568,19 +4583,19 @@
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="22" t="s">
+      <c r="C39" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="44" t="s">
+      <c r="F39" s="46" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4588,54 +4603,54 @@
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="53"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="51"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="53"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="53"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="51"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="53"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="53"/>
-      <c r="C42" s="32" t="s">
+      <c r="B42" s="55"/>
+      <c r="C42" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="51"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="53"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="52"/>
+      <c r="B43" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="54"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="46"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="48"/>
       <c r="F44" s="7"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -4665,96 +4680,75 @@
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="44" t="s">
+      <c r="B48" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="45"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="50"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="50"/>
-      <c r="F51" s="50"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="45"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="50"/>
-      <c r="F52" s="50"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="46"/>
-      <c r="C53" s="49"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="D12:D14"/>
@@ -4765,15 +4759,36 @@
     <mergeCell ref="C15:C17"/>
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="E16:E17"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="F48:F53"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="portrait" r:id="rId1"/>

--- a/Horarios/HorarioWAN_2025.xlsx
+++ b/Horarios/HorarioWAN_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L00614578\Documents\Github\WAN\Horarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39407BD-C2D2-4C48-BEE3-65224C35A173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EB90D8-7D72-4310-9414-425D1072C1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -599,6 +599,69 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -608,15 +671,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -629,9 +683,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -647,94 +698,43 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2014,19 +2014,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="31" t="s">
+      <c r="C3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="31" t="s">
+      <c r="F3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2053,11 +2053,11 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="31"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="14"/>
       <c r="I4" s="2" t="s">
         <v>50</v>
       </c>
@@ -2073,11 +2073,11 @@
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="32" t="s">
+      <c r="C5" s="11"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="11" t="s">
         <v>36</v>
       </c>
       <c r="N5" t="s">
@@ -2092,38 +2092,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="31" t="s">
+      <c r="E6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="32"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
@@ -2153,19 +2153,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="40" t="s">
+      <c r="C12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="32" t="s">
+      <c r="F12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -2183,11 +2183,11 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="32"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="11"/>
       <c r="N13" t="s">
         <v>23</v>
       </c>
@@ -2199,15 +2199,15 @@
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="11" t="s">
+      <c r="D14" s="19"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="30" t="s">
         <v>37</v>
       </c>
       <c r="N14" t="s">
@@ -2222,13 +2222,13 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="40" t="s">
+      <c r="C15" s="18"/>
+      <c r="D15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="38"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="30"/>
       <c r="N15" t="s">
         <v>24</v>
       </c>
@@ -2240,22 +2240,22 @@
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="38"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="30"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="16"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.35">
@@ -2291,19 +2291,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="14" t="s">
+      <c r="D21" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -2333,11 +2333,11 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="33"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="23"/>
       <c r="I22" s="2"/>
       <c r="N22" t="s">
         <v>20</v>
@@ -2351,13 +2351,13 @@
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="29" t="s">
+      <c r="C23" s="37"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="33"/>
+      <c r="G23" s="23"/>
       <c r="N23" t="s">
         <v>24</v>
       </c>
@@ -2370,32 +2370,32 @@
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="11" t="s">
+      <c r="C24" s="37"/>
+      <c r="D24" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="33"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="23"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="34"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="24"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.35">
@@ -2431,19 +2431,19 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="11" t="s">
+      <c r="C30" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>36</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -2467,11 +2467,11 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="33"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="23"/>
       <c r="N31" t="s">
         <v>20</v>
       </c>
@@ -2484,17 +2484,17 @@
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="35" t="s">
+      <c r="D32" s="42"/>
+      <c r="E32" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="23"/>
       <c r="N32" t="s">
         <v>24</v>
       </c>
@@ -2507,32 +2507,32 @@
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="11" t="s">
+      <c r="C33" s="33"/>
+      <c r="D33" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="33"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="23"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="34"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="24"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="37"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="27"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.35">
@@ -2568,19 +2568,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="39" t="s">
+      <c r="D39" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="G39" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -2610,11 +2610,11 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="12"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="23"/>
       <c r="I40" s="2" t="s">
         <v>51</v>
       </c>
@@ -2629,13 +2629,13 @@
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="12"/>
-      <c r="D41" s="29" t="s">
+      <c r="C41" s="33"/>
+      <c r="D41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="33"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="23"/>
       <c r="I41" s="2" t="s">
         <v>52</v>
       </c>
@@ -2651,11 +2651,11 @@
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="13"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="33"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="23"/>
       <c r="T42">
         <f>SUM(T3:T39)</f>
         <v>12</v>
@@ -2665,13 +2665,13 @@
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="30"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="34"/>
+      <c r="C43" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="29"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="24"/>
       <c r="O43">
         <f>SUM(O3:O41)</f>
         <v>110</v>
@@ -2681,10 +2681,10 @@
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="24"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.35">
@@ -2739,34 +2739,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F17"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="E21:E26"/>
     <mergeCell ref="C21:C26"/>
@@ -2782,6 +2754,34 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="D41:D44"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="40" orientation="portrait" r:id="rId1"/>
@@ -2836,19 +2836,19 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="31" t="s">
+      <c r="B3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I3" t="s">
@@ -2860,7 +2860,7 @@
       <c r="L3">
         <v>1</v>
       </c>
-      <c r="N3" s="31" t="s">
+      <c r="N3" s="14" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2868,27 +2868,27 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="31"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14"/>
       <c r="L4" t="s">
         <v>69</v>
       </c>
-      <c r="N4" s="41"/>
+      <c r="N4" s="13"/>
     </row>
     <row r="5" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="14" t="s">
+      <c r="C5" s="13"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="22" t="s">
         <v>22</v>
       </c>
       <c r="H5" t="s">
@@ -2897,28 +2897,28 @@
       <c r="J5" t="s">
         <v>55</v>
       </c>
-      <c r="N5" s="41"/>
+      <c r="N5" s="13"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="31" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="31" t="s">
+      <c r="D6" s="21"/>
+      <c r="E6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="43"/>
+      <c r="F6" s="21"/>
       <c r="J6" t="s">
         <v>73</v>
       </c>
       <c r="L6">
         <v>4</v>
       </c>
-      <c r="N6" s="42" t="s">
+      <c r="N6" s="12" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2926,25 +2926,25 @@
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="24"/>
-      <c r="N7" s="41"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="41"/>
+      <c r="N7" s="13"/>
     </row>
     <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="41"/>
+      <c r="E8" s="13"/>
       <c r="F8" s="6"/>
-      <c r="N8" s="41"/>
+      <c r="N8" s="13"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
@@ -2973,19 +2973,19 @@
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="31" t="s">
+      <c r="B12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="32" t="s">
+      <c r="E12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2993,23 +2993,25 @@
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="32"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="31" t="s">
+      <c r="C14" s="19"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3017,36 +3019,34 @@
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="40" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="31"/>
+      <c r="D15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="31"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="14"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="28"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="7"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -3082,19 +3082,19 @@
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="14" t="s">
+      <c r="B21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="22" t="s">
         <v>68</v>
       </c>
       <c r="H21" t="s">
@@ -3117,58 +3117,58 @@
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="33"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="23"/>
     </row>
     <row r="23" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="29" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="33"/>
+      <c r="F23" s="23"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="11" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="33"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="23"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="34"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="29"/>
+      <c r="F25" s="24"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="16"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="19"/>
       <c r="F26" s="7"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
@@ -3207,19 +3207,19 @@
       <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="11" t="s">
+      <c r="B30" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="14" t="s">
+      <c r="E30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="22" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
@@ -3236,58 +3236,58 @@
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="33"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="23"/>
     </row>
     <row r="32" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="44" t="s">
+      <c r="C32" s="42"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="33"/>
+      <c r="F32" s="23"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="11" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="45"/>
-      <c r="F33" s="33"/>
+      <c r="D33" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="56"/>
+      <c r="F33" s="23"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="34"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="24"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="23"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="40"/>
       <c r="F35" s="7"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
@@ -3323,19 +3323,19 @@
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="14" t="s">
+      <c r="C39" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="46" t="s">
+      <c r="E39" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="46" t="s">
+      <c r="F39" s="44" t="s">
         <v>26</v>
       </c>
       <c r="H39" t="s">
@@ -3355,54 +3355,54 @@
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="55"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="53"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="51"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="55"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="53"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="51"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="55"/>
-      <c r="C42" s="11" t="s">
+      <c r="B42" s="53"/>
+      <c r="C42" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="53"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="51"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="12"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="54"/>
+      <c r="B43" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="33"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="52"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="56"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="48"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="46"/>
       <c r="F44" s="7"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
@@ -3432,13 +3432,13 @@
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="46" t="s">
+      <c r="B48" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
       <c r="L48">
         <f>SUM(L3:L39)</f>
         <v>15</v>
@@ -3448,54 +3448,95 @@
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="47"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="50"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="47"/>
-      <c r="C50" s="50"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="52"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="48"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="47"/>
-      <c r="C51" s="50"/>
-      <c r="D51" s="50"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="47"/>
-      <c r="C52" s="50"/>
-      <c r="D52" s="50"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="48"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="48"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
+      <c r="B53" s="46"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="B43:B44"/>
     <mergeCell ref="N3:N5"/>
     <mergeCell ref="N6:N8"/>
     <mergeCell ref="D39:D44"/>
@@ -3506,47 +3547,6 @@
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="F5:F7"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D3:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3597,19 +3597,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="31" t="s">
+      <c r="C3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="31" t="s">
+      <c r="F3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2"/>
@@ -3618,22 +3618,22 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="32"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="31"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="14"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="32"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="32" t="s">
+      <c r="C5" s="11"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3641,38 +3641,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="31" t="s">
+      <c r="E6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="32"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
@@ -3702,19 +3702,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="40" t="s">
+      <c r="C12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="32" t="s">
+      <c r="F12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="2"/>
@@ -3723,25 +3723,25 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="32"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="11"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="40" t="s">
+      <c r="C14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="11" t="s">
+      <c r="D14" s="19"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="38" t="s">
+      <c r="G14" s="30" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3749,34 +3749,34 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="40" t="s">
+      <c r="C15" s="18"/>
+      <c r="D15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="38"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="30"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="38"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="30"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="16"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="19"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
@@ -3806,19 +3806,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="14" t="s">
+      <c r="D21" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="14" t="s">
+      <c r="F21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2"/>
@@ -3827,55 +3827,55 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="33"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="23"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="29" t="s">
+      <c r="C23" s="37"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="33"/>
+      <c r="G23" s="23"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="19"/>
-      <c r="D24" s="11" t="s">
+      <c r="C24" s="37"/>
+      <c r="D24" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="33"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="23"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="34"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="24"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
@@ -3905,19 +3905,19 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="11" t="s">
+      <c r="C30" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="14" t="s">
+      <c r="F30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>36</v>
       </c>
       <c r="I30" s="2"/>
@@ -3926,58 +3926,58 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="33"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="23"/>
     </row>
     <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="35" t="s">
+      <c r="D32" s="42"/>
+      <c r="E32" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="23"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="11" t="s">
+      <c r="C33" s="33"/>
+      <c r="D33" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="33"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="23"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="34"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="24"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="37"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="27"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
@@ -4007,19 +4007,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="39" t="s">
+      <c r="C39" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="G39" s="22" t="s">
         <v>35</v>
       </c>
       <c r="I39" s="2"/>
@@ -4028,60 +4028,87 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="56"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="33"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="43"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="23"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="33"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="23"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="30"/>
-      <c r="D42" s="11" t="s">
+      <c r="C42" s="29"/>
+      <c r="D42" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="33"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="23"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="30"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="34"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="24"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="16"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
       <c r="G44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
     <mergeCell ref="G39:G43"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D30:D32"/>
@@ -4098,33 +4125,6 @@
     <mergeCell ref="C41:C44"/>
     <mergeCell ref="E39:E44"/>
     <mergeCell ref="F39:F44"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4175,19 +4175,19 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="31" t="s">
+      <c r="B3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4195,23 +4195,23 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="31"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="14"/>
     </row>
     <row r="5" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="14" t="s">
+      <c r="C5" s="13"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="22" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4219,36 +4219,36 @@
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="43"/>
-      <c r="C6" s="31" t="s">
+      <c r="B6" s="21"/>
+      <c r="C6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="43"/>
-      <c r="E6" s="31" t="s">
+      <c r="D6" s="21"/>
+      <c r="E6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="43"/>
+      <c r="F6" s="21"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="24"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="41"/>
     </row>
     <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="13"/>
       <c r="D8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="41"/>
+      <c r="E8" s="13"/>
       <c r="F8" s="6"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -4278,19 +4278,19 @@
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="31" t="s">
+      <c r="B12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="32" t="s">
+      <c r="E12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4298,23 +4298,25 @@
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="32"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="31" t="s">
+      <c r="C14" s="19"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4322,36 +4324,34 @@
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="40" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="43"/>
-      <c r="F15" s="31"/>
+      <c r="D15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="31"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="14"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="28"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="7"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -4381,19 +4381,19 @@
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="14" t="s">
+      <c r="B21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="22" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4401,58 +4401,58 @@
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="33"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="23"/>
     </row>
     <row r="23" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="29" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="33"/>
+      <c r="F23" s="23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="11" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="24"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="33"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="23"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="34"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="29"/>
+      <c r="F25" s="24"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="16"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="19"/>
       <c r="F26" s="7"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -4482,19 +4482,19 @@
       <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="11" t="s">
+      <c r="B30" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="14" t="s">
+      <c r="E30" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="22" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4502,58 +4502,58 @@
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="26"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="33"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="23"/>
     </row>
     <row r="32" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="44" t="s">
+      <c r="C32" s="42"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="33"/>
+      <c r="F32" s="23"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="11" t="s">
+      <c r="B33" s="33"/>
+      <c r="C33" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="45"/>
-      <c r="F33" s="33"/>
+      <c r="D33" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="56"/>
+      <c r="F33" s="23"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="34"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="24"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="23"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="40"/>
       <c r="F35" s="7"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -4583,19 +4583,19 @@
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="14" t="s">
+      <c r="C39" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="46" t="s">
+      <c r="E39" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="46" t="s">
+      <c r="F39" s="44" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4603,54 +4603,54 @@
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="55"/>
-      <c r="C40" s="26"/>
-      <c r="D40" s="33"/>
-      <c r="E40" s="47"/>
-      <c r="F40" s="53"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="43"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="51"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="55"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="47"/>
-      <c r="F41" s="53"/>
+      <c r="B41" s="53"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="51"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="55"/>
-      <c r="C42" s="11" t="s">
+      <c r="B42" s="53"/>
+      <c r="C42" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="33"/>
-      <c r="E42" s="47"/>
-      <c r="F42" s="53"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="51"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="12"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="54"/>
+      <c r="B43" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="33"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="52"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="56"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="48"/>
+      <c r="B44" s="55"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="46"/>
       <c r="F44" s="7"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -4680,66 +4680,106 @@
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="46" t="s">
+      <c r="B48" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="49"/>
-      <c r="D48" s="49"/>
-      <c r="E48" s="49"/>
-      <c r="F48" s="49"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="47"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="50"/>
-      <c r="E49" s="52"/>
-      <c r="F49" s="52"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="47"/>
-      <c r="C50" s="50"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="52"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="48"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="47"/>
-      <c r="C51" s="50"/>
-      <c r="D51" s="50"/>
-      <c r="E51" s="52"/>
-      <c r="F51" s="52"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="47"/>
-      <c r="C52" s="50"/>
-      <c r="D52" s="50"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="48"/>
+      <c r="D52" s="48"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="48"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
+      <c r="B53" s="46"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="49"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="F48:F53"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E17"/>
     <mergeCell ref="B5:B8"/>
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="C6:C8"/>
@@ -4749,46 +4789,6 @@
     <mergeCell ref="D3:D7"/>
     <mergeCell ref="E3:E5"/>
     <mergeCell ref="F3:F4"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="F48:F53"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="portrait" r:id="rId1"/>

--- a/Horarios/HorarioWAN_2025.xlsx
+++ b/Horarios/HorarioWAN_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L00614578\Documents\Github\WAN\Horarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37EB90D8-7D72-4310-9414-425D1072C1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94AD6931-3D88-4E49-94F2-F309493B2749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{85581F8A-1D8C-4874-8F74-82FACFEFF46D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -599,103 +599,109 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -728,13 +734,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2014,19 +2014,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="C3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="31" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2053,11 +2053,11 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="31"/>
       <c r="I4" s="2" t="s">
         <v>50</v>
       </c>
@@ -2073,11 +2073,11 @@
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="11" t="s">
+      <c r="C5" s="32"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="32" t="s">
         <v>36</v>
       </c>
       <c r="N5" t="s">
@@ -2092,38 +2092,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="14" t="s">
+      <c r="E6" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="11"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="32"/>
     </row>
     <row r="8" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:20" x14ac:dyDescent="0.35">
@@ -2153,19 +2153,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="C12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="11" t="s">
+      <c r="F12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="32" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -2183,11 +2183,11 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="11"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="32"/>
       <c r="N13" t="s">
         <v>23</v>
       </c>
@@ -2199,15 +2199,15 @@
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="32" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="38" t="s">
         <v>37</v>
       </c>
       <c r="N14" t="s">
@@ -2222,13 +2222,13 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="17" t="s">
+      <c r="C15" s="15"/>
+      <c r="D15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="30"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="38"/>
       <c r="N15" t="s">
         <v>24</v>
       </c>
@@ -2240,22 +2240,22 @@
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="30"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="38"/>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="19"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="16"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.35">
@@ -2291,19 +2291,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="22" t="s">
+      <c r="D21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="22" t="s">
+      <c r="F21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2" t="s">
@@ -2333,11 +2333,11 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="33"/>
       <c r="I22" s="2"/>
       <c r="N22" t="s">
         <v>20</v>
@@ -2351,13 +2351,13 @@
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="28" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="33"/>
       <c r="N23" t="s">
         <v>24</v>
       </c>
@@ -2370,32 +2370,32 @@
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="19"/>
+      <c r="D24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="23"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="33"/>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="24"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="34"/>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.35">
@@ -2431,19 +2431,19 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="32" t="s">
+      <c r="C30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="22" t="s">
+      <c r="F30" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I30" s="2" t="s">
@@ -2467,11 +2467,11 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="23"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="33"/>
       <c r="N31" t="s">
         <v>20</v>
       </c>
@@ -2484,17 +2484,17 @@
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="42"/>
-      <c r="E32" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="25" t="s">
+      <c r="D32" s="25"/>
+      <c r="E32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="23"/>
+      <c r="G32" s="33"/>
       <c r="N32" t="s">
         <v>24</v>
       </c>
@@ -2507,32 +2507,32 @@
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="32" t="s">
+      <c r="C33" s="12"/>
+      <c r="D33" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="23"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="33"/>
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="24"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="34"/>
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="27"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="37"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.35">
@@ -2568,19 +2568,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="31" t="s">
+      <c r="D39" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I39" s="2" t="s">
@@ -2610,11 +2610,11 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="33"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="23"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="33"/>
       <c r="I40" s="2" t="s">
         <v>51</v>
       </c>
@@ -2629,13 +2629,13 @@
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="33"/>
-      <c r="D41" s="28" t="s">
+      <c r="C41" s="12"/>
+      <c r="D41" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="23"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="33"/>
       <c r="I41" s="2" t="s">
         <v>52</v>
       </c>
@@ -2651,11 +2651,11 @@
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="23"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="33"/>
       <c r="T42">
         <f>SUM(T3:T39)</f>
         <v>12</v>
@@ -2665,13 +2665,13 @@
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D43" s="29"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="24"/>
+      <c r="C43" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="30"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="34"/>
       <c r="O43">
         <f>SUM(O3:O41)</f>
         <v>110</v>
@@ -2681,10 +2681,10 @@
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="41"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
       <c r="G44" s="7"/>
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.35">
@@ -2739,6 +2739,34 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="G39:G43"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="F32:F35"/>
+    <mergeCell ref="G30:G34"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="F39:F44"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F17"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="E21:E26"/>
     <mergeCell ref="C21:C26"/>
@@ -2754,37 +2782,9 @@
     <mergeCell ref="D33:D35"/>
     <mergeCell ref="D39:D40"/>
     <mergeCell ref="D41:D44"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="G39:G43"/>
-    <mergeCell ref="F30:F31"/>
-    <mergeCell ref="F32:F35"/>
-    <mergeCell ref="G30:G34"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="F39:F44"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="40" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="55" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2836,19 +2836,19 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="B3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="31" t="s">
         <v>31</v>
       </c>
       <c r="I3" t="s">
@@ -2860,7 +2860,7 @@
       <c r="L3">
         <v>1</v>
       </c>
-      <c r="N3" s="14" t="s">
+      <c r="N3" s="31" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2868,27 +2868,27 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="31"/>
       <c r="L4" t="s">
         <v>69</v>
       </c>
-      <c r="N4" s="13"/>
+      <c r="N4" s="41"/>
     </row>
     <row r="5" spans="1:14" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="22" t="s">
+      <c r="C5" s="41"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="H5" t="s">
@@ -2897,28 +2897,28 @@
       <c r="J5" t="s">
         <v>55</v>
       </c>
-      <c r="N5" s="13"/>
+      <c r="N5" s="41"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="14" t="s">
+      <c r="D6" s="43"/>
+      <c r="E6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="21"/>
+      <c r="F6" s="43"/>
       <c r="J6" t="s">
         <v>73</v>
       </c>
       <c r="L6">
         <v>4</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="42" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2926,25 +2926,25 @@
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="41"/>
-      <c r="N7" s="13"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="24"/>
+      <c r="N7" s="41"/>
     </row>
     <row r="8" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="13"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="41"/>
       <c r="F8" s="6"/>
-      <c r="N8" s="13"/>
+      <c r="N8" s="41"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
@@ -2973,19 +2973,19 @@
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="14" t="s">
+      <c r="B12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="11" t="s">
+      <c r="E12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="32" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2993,25 +2993,25 @@
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="11"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="32"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="17" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3019,34 +3019,34 @@
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="14"/>
+      <c r="D15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="31"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="31"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="19"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="7"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
@@ -3082,19 +3082,19 @@
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="22" t="s">
+      <c r="B21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>68</v>
       </c>
       <c r="H21" t="s">
@@ -3117,58 +3117,58 @@
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="23"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="33"/>
     </row>
     <row r="23" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="28" t="s">
+      <c r="C23" s="16"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="23"/>
+      <c r="F23" s="33"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="32" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="33"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="24"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="30"/>
+      <c r="F25" s="34"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="19"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="7"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
@@ -3207,19 +3207,19 @@
       <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="32" t="s">
+      <c r="B30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="22" t="s">
+      <c r="E30" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
@@ -3236,58 +3236,58 @@
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="23"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="33"/>
     </row>
     <row r="32" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="54" t="s">
+      <c r="C32" s="25"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="23"/>
+      <c r="F32" s="33"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="12"/>
+      <c r="C33" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="56"/>
-      <c r="F33" s="23"/>
+      <c r="D33" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="45"/>
+      <c r="F33" s="33"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="24"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="34"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="40"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="23"/>
       <c r="F35" s="7"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
@@ -3323,19 +3323,19 @@
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="22" t="s">
+      <c r="C39" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="44" t="s">
+      <c r="F39" s="46" t="s">
         <v>26</v>
       </c>
       <c r="H39" t="s">
@@ -3355,54 +3355,54 @@
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="53"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="51"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="53"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="53"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="51"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="53"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="53"/>
-      <c r="C42" s="32" t="s">
+      <c r="B42" s="55"/>
+      <c r="C42" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="51"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="53"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="52"/>
+      <c r="B43" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="54"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="46"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="48"/>
       <c r="F44" s="7"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
@@ -3432,13 +3432,13 @@
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="44" t="s">
+      <c r="B48" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
       <c r="L48">
         <f>SUM(L3:L39)</f>
         <v>15</v>
@@ -3448,85 +3448,64 @@
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="45"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="50"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="50"/>
-      <c r="F51" s="50"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="45"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="50"/>
-      <c r="F52" s="50"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="46"/>
-      <c r="C53" s="49"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F5:F7"/>
     <mergeCell ref="B48:B53"/>
     <mergeCell ref="C48:C53"/>
     <mergeCell ref="F48:F53"/>
@@ -3537,16 +3516,37 @@
     <mergeCell ref="E48:E53"/>
     <mergeCell ref="B39:B42"/>
     <mergeCell ref="B43:B44"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C15:C17"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="D3:D7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3597,19 +3597,19 @@
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="14" t="s">
+      <c r="C3" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="14" t="s">
+      <c r="F3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="31" t="s">
         <v>31</v>
       </c>
       <c r="I3" s="2"/>
@@ -3618,22 +3618,22 @@
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="31"/>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="11" t="s">
+      <c r="C5" s="32"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="32" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3641,38 +3641,38 @@
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="14" t="s">
+      <c r="E6" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="11"/>
+      <c r="G6" s="32"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="11"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="32"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
       <c r="G8" s="6"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.35">
@@ -3702,19 +3702,19 @@
       <c r="B12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="C12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="11" t="s">
+      <c r="F12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="32" t="s">
         <v>36</v>
       </c>
       <c r="I12" s="2"/>
@@ -3723,25 +3723,25 @@
       <c r="B13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="11"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="32"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="32" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="38" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3749,34 +3749,34 @@
       <c r="B15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="17" t="s">
+      <c r="C15" s="15"/>
+      <c r="D15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="30"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="38"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="30"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="15"/>
+      <c r="G16" s="38"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="19"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="16"/>
       <c r="G17" s="7"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.35">
@@ -3806,19 +3806,19 @@
       <c r="B21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="22" t="s">
+      <c r="D21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G21" s="22" t="s">
+      <c r="F21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" s="14" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="2"/>
@@ -3827,55 +3827,55 @@
       <c r="B22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="23"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="33"/>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="28" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G23" s="23"/>
+      <c r="G23" s="33"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="32" t="s">
+      <c r="C24" s="19"/>
+      <c r="D24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E24" s="18"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="23"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="33"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="24"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="34"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="38"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
       <c r="G26" s="7"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.35">
@@ -3905,19 +3905,19 @@
       <c r="B30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="32" t="s">
+      <c r="C30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G30" s="22" t="s">
+      <c r="F30" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I30" s="2"/>
@@ -3926,58 +3926,58 @@
       <c r="B31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="42"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="23"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="33"/>
     </row>
     <row r="32" spans="2:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="42"/>
-      <c r="E32" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="25" t="s">
+      <c r="D32" s="25"/>
+      <c r="E32" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="23"/>
+      <c r="G32" s="33"/>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="33"/>
-      <c r="D33" s="32" t="s">
+      <c r="C33" s="12"/>
+      <c r="D33" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="39"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="23"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="33"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="24"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="34"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="27"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="37"/>
       <c r="G35" s="7"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.35">
@@ -4007,19 +4007,19 @@
       <c r="B39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C39" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="31" t="s">
+      <c r="C39" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G39" s="14" t="s">
         <v>35</v>
       </c>
       <c r="I39" s="2"/>
@@ -4028,87 +4028,60 @@
       <c r="B40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C40" s="55"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="23"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="33"/>
       <c r="I40" s="2"/>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="28" t="s">
+      <c r="C41" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="D41" s="42"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="23"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="33"/>
       <c r="I41" s="2"/>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C42" s="29"/>
-      <c r="D42" s="32" t="s">
+      <c r="C42" s="30"/>
+      <c r="D42" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="23"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="33"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="29"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="24"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="34"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
       <c r="G44" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E15"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G16"/>
-    <mergeCell ref="D15:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="D21:D23"/>
-    <mergeCell ref="E21:E26"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="D24:D26"/>
     <mergeCell ref="G39:G43"/>
     <mergeCell ref="C30:C31"/>
     <mergeCell ref="D30:D32"/>
@@ -4125,6 +4098,33 @@
     <mergeCell ref="C41:C44"/>
     <mergeCell ref="E39:E44"/>
     <mergeCell ref="F39:F44"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="E21:E26"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E15"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G16"/>
+    <mergeCell ref="D15:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4175,19 +4175,19 @@
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="14" t="s">
+      <c r="B3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="31" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4195,23 +4195,23 @@
       <c r="A4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="31"/>
     </row>
     <row r="5" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="22" t="s">
+      <c r="C5" s="41"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4219,36 +4219,36 @@
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="14" t="s">
+      <c r="B6" s="43"/>
+      <c r="C6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="14" t="s">
+      <c r="D6" s="43"/>
+      <c r="E6" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="21"/>
+      <c r="F6" s="43"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="41"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="24"/>
     </row>
     <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="13"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="41"/>
       <c r="F8" s="6"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -4278,19 +4278,19 @@
       <c r="A12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="14" t="s">
+      <c r="B12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="11" t="s">
+      <c r="E12" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="32" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4298,25 +4298,25 @@
       <c r="A13" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="11"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="32"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="17" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="31" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4324,34 +4324,34 @@
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="14"/>
+      <c r="D15" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="15"/>
+      <c r="F15" s="31"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="14"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="31"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="19"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="7"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -4381,19 +4381,19 @@
       <c r="A21" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F21" s="22" t="s">
+      <c r="B21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4401,58 +4401,58 @@
       <c r="A22" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="23"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="33"/>
     </row>
     <row r="23" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="19"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="28" t="s">
+      <c r="C23" s="16"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="23"/>
+      <c r="F23" s="33"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="32" t="s">
+      <c r="B24" s="15"/>
+      <c r="C24" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="41"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="23"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="33"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="33"/>
-      <c r="D25" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="29"/>
-      <c r="F25" s="24"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="30"/>
+      <c r="F25" s="34"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="19"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="7"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -4482,19 +4482,19 @@
       <c r="A30" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="32" t="s">
+      <c r="B30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E30" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F30" s="22" t="s">
+      <c r="E30" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="14" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4502,58 +4502,58 @@
       <c r="A31" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="42"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="23"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="33"/>
     </row>
     <row r="32" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="54" t="s">
+      <c r="C32" s="25"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="F32" s="23"/>
+      <c r="F32" s="33"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="32" t="s">
+      <c r="B33" s="12"/>
+      <c r="C33" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D33" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="56"/>
-      <c r="F33" s="23"/>
+      <c r="D33" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="45"/>
+      <c r="F33" s="33"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="33"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="24"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="34"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="40"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="24"/>
+      <c r="E35" s="23"/>
       <c r="F35" s="7"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -4583,19 +4583,19 @@
       <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D39" s="22" t="s">
+      <c r="C39" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E39" s="44" t="s">
+      <c r="E39" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="F39" s="44" t="s">
+      <c r="F39" s="46" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4603,54 +4603,54 @@
       <c r="A40" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B40" s="53"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="23"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="51"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="33"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="53"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="53"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="45"/>
-      <c r="F41" s="51"/>
+      <c r="B41" s="55"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="53"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B42" s="53"/>
-      <c r="C42" s="32" t="s">
+      <c r="B42" s="55"/>
+      <c r="C42" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="45"/>
-      <c r="F42" s="51"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="53"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="33"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="45"/>
-      <c r="F43" s="52"/>
+      <c r="B43" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="12"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="54"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="46"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="48"/>
       <c r="F44" s="7"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -4680,96 +4680,75 @@
       <c r="A48" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B48" s="44" t="s">
+      <c r="B48" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="47"/>
-      <c r="D48" s="47"/>
-      <c r="E48" s="47"/>
-      <c r="F48" s="47"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="49"/>
+      <c r="E48" s="49"/>
+      <c r="F48" s="49"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="45"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="50"/>
+      <c r="B50" s="47"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="50"/>
-      <c r="F51" s="50"/>
+      <c r="B51" s="47"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B52" s="45"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="50"/>
-      <c r="F52" s="50"/>
+      <c r="B52" s="47"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B53" s="46"/>
-      <c r="C53" s="49"/>
-      <c r="D53" s="49"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="51"/>
+      <c r="D53" s="51"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="C48:C53"/>
-    <mergeCell ref="D48:D53"/>
-    <mergeCell ref="E48:E53"/>
-    <mergeCell ref="F48:F53"/>
-    <mergeCell ref="B39:B42"/>
-    <mergeCell ref="C39:C41"/>
-    <mergeCell ref="D39:D44"/>
-    <mergeCell ref="E39:E44"/>
-    <mergeCell ref="F39:F43"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="D30:D32"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="F30:F34"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="E32:E35"/>
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="F21:F25"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="E23:E26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C23"/>
-    <mergeCell ref="D21:D24"/>
-    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F4"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="D12:D14"/>
@@ -4780,15 +4759,36 @@
     <mergeCell ref="D15:D17"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="E14:E17"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F21:F25"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="E23:E26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:C23"/>
+    <mergeCell ref="D21:D24"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="D30:D32"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F34"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="E32:E35"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="C39:C41"/>
+    <mergeCell ref="D39:D44"/>
+    <mergeCell ref="E39:E44"/>
+    <mergeCell ref="F39:F43"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="C48:C53"/>
+    <mergeCell ref="D48:D53"/>
+    <mergeCell ref="E48:E53"/>
+    <mergeCell ref="F48:F53"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="portrait" r:id="rId1"/>
